--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\new app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A4F611-D392-4068-8330-D16F37B52C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A89F2BE-9D8D-4ECE-B8A7-FC658821E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Menu-English" sheetId="3" r:id="rId3"/>
     <sheet name="Menu-Arabic" sheetId="5" r:id="rId4"/>
     <sheet name="RelatedItems" sheetId="6" r:id="rId5"/>
+    <sheet name="Image sizes" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="852">
   <si>
     <t>Contact</t>
   </si>
@@ -2487,15 +2488,9 @@
     <t>966 550573095</t>
   </si>
   <si>
-    <t>966 560662785</t>
-  </si>
-  <si>
     <t>Dar al baida, Azizia, Riyadh, KSA</t>
   </si>
   <si>
-    <t>intent://www.google.com/maps/place//data=!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1?entry=s&amp;sa=X&amp;ved=1t:8290&amp;ictx=111#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
-  </si>
-  <si>
     <t>Delivery Free with in 3 KM</t>
   </si>
   <si>
@@ -2505,9 +2500,6 @@
     <t>http:/www.instagram.com/usthad_azizia/</t>
   </si>
   <si>
-    <t>usthad2024@gmail.com</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/banner/Banner04.jpg</t>
   </si>
   <si>
@@ -2521,13 +2513,100 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/banner/Banner02.jpg</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
+  </si>
+  <si>
+    <t>Image Type</t>
+  </si>
+  <si>
+    <t>Aspect Ratio</t>
+  </si>
+  <si>
+    <t>Recommended Size</t>
+  </si>
+  <si>
+    <t>Best Format</t>
+  </si>
+  <si>
+    <t>Brand Logo / PWA Icon</t>
+  </si>
+  <si>
+    <t>1:1 (Square)</t>
+  </si>
+  <si>
+    <t>512 x 512 px</t>
+  </si>
+  <si>
+    <t>PNG / WebP</t>
+  </si>
+  <si>
+    <t>&lt; 100 KB</t>
+  </si>
+  <si>
+    <t>Menu Items (Food Grid)</t>
+  </si>
+  <si>
+    <t>4:3 (Landscape)</t>
+  </si>
+  <si>
+    <t>800 x 600 px</t>
+  </si>
+  <si>
+    <t>WebP / JPG</t>
+  </si>
+  <si>
+    <t>Quick Access Icons</t>
+  </si>
+  <si>
+    <t>300 x 300 px</t>
+  </si>
+  <si>
+    <t>&lt; 50 KB</t>
+  </si>
+  <si>
+    <t>Top Promo Banners</t>
+  </si>
+  <si>
+    <t>2:1 (Wide)</t>
+  </si>
+  <si>
+    <t>1200 x 600 px</t>
+  </si>
+  <si>
+    <t>&lt; 200 KB</t>
+  </si>
+  <si>
+    <t>Category Break Banners</t>
+  </si>
+  <si>
+    <t>3:1 (Ultra-Wide)</t>
+  </si>
+  <si>
+    <t>1200 x 400 px</t>
+  </si>
+  <si>
+    <t>&lt; 150 KB</t>
+  </si>
+  <si>
+    <t>Idle Flashcard Popups</t>
+  </si>
+  <si>
+    <t>4:5 (Portrait)</t>
+  </si>
+  <si>
+    <t>1080 x 1350 px</t>
+  </si>
+  <si>
+    <t>Max File Size recommended</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2585,6 +2664,19 @@
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2652,7 +2744,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2697,6 +2789,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2834,6 +2932,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3191,7 +3293,7 @@
     <col min="11" max="12" width="9.9453125" customWidth="1"/>
     <col min="13" max="13" width="13.20703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="67.41796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.20703125" customWidth="1"/>
+    <col min="15" max="15" width="39.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -3257,35 +3359,30 @@
       <c r="D2" t="s">
         <v>122</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2"/>
+      <c r="H2" t="s">
         <v>814</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="H2" t="s">
-        <v>815</v>
-      </c>
       <c r="I2" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="K2" t="s">
         <v>816</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="K2" t="s">
-        <v>818</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
       <c r="M2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3326,6 +3423,7 @@
     <hyperlink ref="O3" r:id="rId1" tooltip="Banner02.jpg" display="https://github.com/Rmoosa2014/Restaurant-menu/blob/main/images/banner/Banner02.jpg" xr:uid="{1AA01F29-999B-4367-883C-4232785B746E}"/>
     <hyperlink ref="N2" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/KARAK-WA-KARAK/main/logo.png" xr:uid="{A1FB07C3-B8F2-49A0-A23A-B1A95E6708A3}"/>
     <hyperlink ref="O2" r:id="rId3" display="https://raw.githubusercontent.com/DigiDatas/ShawarMax-Al-Manar/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/DigiDatas/ShawarMax-Al-Manar/main/images/banner/Banner02.jpg" xr:uid="{81AFF1C3-240D-468E-995A-5B6703C1D34C}"/>
+    <hyperlink ref="I2" r:id="rId4" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{D3138493-AF89-421B-991A-F6B48A9858C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3371,10 +3469,10 @@
         <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3388,7 +3486,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3402,7 +3500,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3528,7 +3626,7 @@
         <v>133</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>134</v>
@@ -3573,7 +3671,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>136</v>
@@ -3620,7 +3718,7 @@
         <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>138</v>
@@ -3665,7 +3763,7 @@
         <v>133</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>140</v>
@@ -3710,7 +3808,7 @@
         <v>133</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>142</v>
@@ -3757,7 +3855,7 @@
         <v>133</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>144</v>
@@ -3802,7 +3900,7 @@
         <v>133</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>146</v>
@@ -3850,7 +3948,7 @@
         <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>148</v>
@@ -3895,7 +3993,7 @@
         <v>133</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>151</v>
@@ -3940,7 +4038,7 @@
         <v>133</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>153</v>
@@ -3985,7 +4083,7 @@
         <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>156</v>
@@ -4030,7 +4128,7 @@
         <v>133</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>158</v>
@@ -4075,7 +4173,7 @@
         <v>133</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>161</v>
@@ -4120,7 +4218,7 @@
         <v>165</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>166</v>
@@ -4168,7 +4266,7 @@
         <v>165</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>169</v>
@@ -4209,7 +4307,7 @@
         <v>165</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>172</v>
@@ -4250,7 +4348,7 @@
         <v>165</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>175</v>
@@ -4291,7 +4389,7 @@
         <v>165</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>178</v>
@@ -4334,7 +4432,7 @@
         <v>165</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>181</v>
@@ -4375,7 +4473,7 @@
         <v>165</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>184</v>
@@ -4416,7 +4514,7 @@
         <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>188</v>
@@ -4457,7 +4555,7 @@
         <v>165</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>191</v>
@@ -4503,7 +4601,7 @@
         <v>165</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>194</v>
@@ -4544,7 +4642,7 @@
         <v>165</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>197</v>
@@ -4589,7 +4687,7 @@
         <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>199</v>
@@ -4634,7 +4732,7 @@
         <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>202</v>
@@ -4675,7 +4773,7 @@
         <v>165</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>205</v>
@@ -4716,7 +4814,7 @@
         <v>165</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>208</v>
@@ -4757,7 +4855,7 @@
         <v>165</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>213</v>
@@ -4798,7 +4896,7 @@
         <v>165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>216</v>
@@ -4839,7 +4937,7 @@
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>219</v>
@@ -4880,7 +4978,7 @@
         <v>165</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>222</v>
@@ -4921,7 +5019,7 @@
         <v>165</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>225</v>
@@ -4962,7 +5060,7 @@
         <v>165</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>228</v>
@@ -5003,7 +5101,7 @@
         <v>165</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>231</v>
@@ -5044,7 +5142,7 @@
         <v>165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>235</v>
@@ -5085,7 +5183,7 @@
         <v>165</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>238</v>
@@ -5128,7 +5226,7 @@
         <v>165</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>241</v>
@@ -5169,7 +5267,7 @@
         <v>165</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>246</v>
@@ -5210,7 +5308,7 @@
         <v>165</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>249</v>
@@ -5251,7 +5349,7 @@
         <v>165</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>252</v>
@@ -5294,7 +5392,7 @@
         <v>165</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>255</v>
@@ -5335,7 +5433,7 @@
         <v>165</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>197</v>
@@ -5376,7 +5474,7 @@
         <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>261</v>
@@ -5417,7 +5515,7 @@
         <v>165</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>264</v>
@@ -5458,7 +5556,7 @@
         <v>165</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>268</v>
@@ -5499,7 +5597,7 @@
         <v>273</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>274</v>
@@ -5540,7 +5638,7 @@
         <v>273</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>277</v>
@@ -5581,7 +5679,7 @@
         <v>273</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>281</v>
@@ -5625,7 +5723,7 @@
         <v>273</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>277</v>
@@ -5668,7 +5766,7 @@
         <v>273</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>286</v>
@@ -5709,7 +5807,7 @@
         <v>273</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>289</v>
@@ -5750,7 +5848,7 @@
         <v>273</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>292</v>
@@ -5791,7 +5889,7 @@
         <v>273</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>295</v>
@@ -5832,7 +5930,7 @@
         <v>273</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>298</v>
@@ -5873,7 +5971,7 @@
         <v>273</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>302</v>
@@ -5914,7 +6012,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>305</v>
@@ -5955,7 +6053,7 @@
         <v>273</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>308</v>
@@ -5996,7 +6094,7 @@
         <v>273</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>311</v>
@@ -6039,7 +6137,7 @@
         <v>273</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>314</v>
@@ -6080,7 +6178,7 @@
         <v>273</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>317</v>
@@ -6121,7 +6219,7 @@
         <v>273</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>321</v>
@@ -6162,7 +6260,7 @@
         <v>273</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>324</v>
@@ -6203,7 +6301,7 @@
         <v>273</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>327</v>
@@ -6244,7 +6342,7 @@
         <v>331</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>332</v>
@@ -6289,7 +6387,7 @@
         <v>331</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>334</v>
@@ -6334,7 +6432,7 @@
         <v>331</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>336</v>
@@ -6382,7 +6480,7 @@
         <v>331</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>338</v>
@@ -6429,7 +6527,7 @@
         <v>331</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>338</v>
@@ -6476,7 +6574,7 @@
         <v>331</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>342</v>
@@ -6521,7 +6619,7 @@
         <v>331</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>345</v>
@@ -6568,7 +6666,7 @@
         <v>331</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>345</v>
@@ -6615,7 +6713,7 @@
         <v>331</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>347</v>
@@ -6662,7 +6760,7 @@
         <v>331</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>347</v>
@@ -6709,7 +6807,7 @@
         <v>331</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>349</v>
@@ -6756,7 +6854,7 @@
         <v>331</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>349</v>
@@ -6803,7 +6901,7 @@
         <v>331</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>351</v>
@@ -6850,7 +6948,7 @@
         <v>331</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>351</v>
@@ -6897,7 +6995,7 @@
         <v>331</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>353</v>
@@ -6944,7 +7042,7 @@
         <v>331</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>353</v>
@@ -6991,7 +7089,7 @@
         <v>331</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>355</v>
@@ -7038,7 +7136,7 @@
         <v>331</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>355</v>
@@ -7085,7 +7183,7 @@
         <v>331</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>358</v>
@@ -7130,7 +7228,7 @@
         <v>361</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>363</v>
@@ -7171,7 +7269,7 @@
         <v>361</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>366</v>
@@ -7212,7 +7310,7 @@
         <v>361</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>369</v>
@@ -7253,7 +7351,7 @@
         <v>361</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>372</v>
@@ -7294,7 +7392,7 @@
         <v>361</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>375</v>
@@ -7335,7 +7433,7 @@
         <v>361</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>379</v>
@@ -7376,7 +7474,7 @@
         <v>361</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>382</v>
@@ -7417,7 +7515,7 @@
         <v>387</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>388</v>
@@ -7458,7 +7556,7 @@
         <v>387</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>391</v>
@@ -7499,7 +7597,7 @@
         <v>387</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>394</v>
@@ -7540,7 +7638,7 @@
         <v>387</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>398</v>
@@ -7583,7 +7681,7 @@
         <v>387</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>398</v>
@@ -7626,7 +7724,7 @@
         <v>387</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>398</v>
@@ -7669,7 +7767,7 @@
         <v>387</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>402</v>
@@ -7712,7 +7810,7 @@
         <v>387</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>402</v>
@@ -7755,7 +7853,7 @@
         <v>387</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F100" s="12" t="s">
         <v>402</v>
@@ -7798,7 +7896,7 @@
         <v>387</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>405</v>
@@ -7841,7 +7939,7 @@
         <v>387</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>405</v>
@@ -7886,7 +7984,7 @@
         <v>387</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F103" s="12" t="s">
         <v>405</v>
@@ -7929,7 +8027,7 @@
         <v>387</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F104" s="12" t="s">
         <v>408</v>
@@ -7975,7 +8073,7 @@
         <v>387</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>408</v>
@@ -8018,7 +8116,7 @@
         <v>387</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>408</v>
@@ -8061,7 +8159,7 @@
         <v>387</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F107" s="12" t="s">
         <v>411</v>
@@ -8104,7 +8202,7 @@
         <v>387</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F108" s="12" t="s">
         <v>411</v>
@@ -8147,7 +8245,7 @@
         <v>387</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>411</v>
@@ -8190,7 +8288,7 @@
         <v>387</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F110" s="12" t="s">
         <v>414</v>
@@ -8233,7 +8331,7 @@
         <v>387</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>414</v>
@@ -8276,7 +8374,7 @@
         <v>387</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F112" s="12" t="s">
         <v>414</v>
@@ -8319,7 +8417,7 @@
         <v>387</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F113" s="12" t="s">
         <v>417</v>
@@ -8362,7 +8460,7 @@
         <v>387</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F114" s="12" t="s">
         <v>417</v>
@@ -8405,7 +8503,7 @@
         <v>387</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>417</v>
@@ -8448,7 +8546,7 @@
         <v>387</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F116" s="12" t="s">
         <v>420</v>
@@ -8491,7 +8589,7 @@
         <v>387</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F117" s="12" t="s">
         <v>420</v>
@@ -8534,7 +8632,7 @@
         <v>387</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>420</v>
@@ -8577,7 +8675,7 @@
         <v>387</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>423</v>
@@ -8620,7 +8718,7 @@
         <v>387</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F120" s="12" t="s">
         <v>423</v>
@@ -8663,7 +8761,7 @@
         <v>387</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F121" s="12" t="s">
         <v>423</v>
@@ -8706,7 +8804,7 @@
         <v>387</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F122" s="12" t="s">
         <v>426</v>
@@ -8749,7 +8847,7 @@
         <v>387</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F123" s="12" t="s">
         <v>426</v>
@@ -8792,7 +8890,7 @@
         <v>387</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F124" s="12" t="s">
         <v>426</v>
@@ -8835,7 +8933,7 @@
         <v>387</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F125" s="12" t="s">
         <v>429</v>
@@ -8878,7 +8976,7 @@
         <v>387</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F126" s="12" t="s">
         <v>429</v>
@@ -8921,7 +9019,7 @@
         <v>387</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F127" s="12" t="s">
         <v>429</v>
@@ -8964,7 +9062,7 @@
         <v>387</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F128" s="12" t="s">
         <v>432</v>
@@ -9007,7 +9105,7 @@
         <v>387</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F129" s="12" t="s">
         <v>432</v>
@@ -9050,7 +9148,7 @@
         <v>387</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F130" s="12" t="s">
         <v>432</v>
@@ -9093,7 +9191,7 @@
         <v>387</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F131" s="12" t="s">
         <v>435</v>
@@ -9136,7 +9234,7 @@
         <v>387</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>435</v>
@@ -9179,7 +9277,7 @@
         <v>387</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>435</v>
@@ -9222,7 +9320,7 @@
         <v>387</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F134" s="12" t="s">
         <v>439</v>
@@ -9265,7 +9363,7 @@
         <v>387</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F135" s="12" t="s">
         <v>439</v>
@@ -9308,7 +9406,7 @@
         <v>387</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F136" s="12" t="s">
         <v>439</v>
@@ -9351,7 +9449,7 @@
         <v>387</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F137" s="12" t="s">
         <v>442</v>
@@ -9394,7 +9492,7 @@
         <v>387</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F138" s="12" t="s">
         <v>442</v>
@@ -9437,7 +9535,7 @@
         <v>387</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F139" s="12" t="s">
         <v>442</v>
@@ -9480,7 +9578,7 @@
         <v>387</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F140" s="12" t="s">
         <v>445</v>
@@ -9523,7 +9621,7 @@
         <v>387</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F141" s="12" t="s">
         <v>445</v>
@@ -9566,7 +9664,7 @@
         <v>387</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F142" s="12" t="s">
         <v>445</v>
@@ -9609,7 +9707,7 @@
         <v>387</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F143" s="12" t="s">
         <v>449</v>
@@ -9652,7 +9750,7 @@
         <v>387</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F144" s="12" t="s">
         <v>449</v>
@@ -9695,7 +9793,7 @@
         <v>387</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>449</v>
@@ -9738,7 +9836,7 @@
         <v>387</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F146" s="12" t="s">
         <v>452</v>
@@ -9781,7 +9879,7 @@
         <v>387</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>452</v>
@@ -9824,7 +9922,7 @@
         <v>387</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>452</v>
@@ -9867,7 +9965,7 @@
         <v>387</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>455</v>
@@ -9910,7 +10008,7 @@
         <v>387</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>455</v>
@@ -9953,7 +10051,7 @@
         <v>387</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>455</v>
@@ -9996,7 +10094,7 @@
         <v>460</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F152" s="12" t="s">
         <v>461</v>
@@ -10039,7 +10137,7 @@
         <v>460</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>461</v>
@@ -10085,7 +10183,7 @@
         <v>460</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>464</v>
@@ -10128,7 +10226,7 @@
         <v>460</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F155" s="12" t="s">
         <v>464</v>
@@ -10171,7 +10269,7 @@
         <v>460</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>467</v>
@@ -10214,7 +10312,7 @@
         <v>460</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>467</v>
@@ -10257,7 +10355,7 @@
         <v>460</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F158" s="12" t="s">
         <v>470</v>
@@ -10300,7 +10398,7 @@
         <v>460</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F159" s="12" t="s">
         <v>470</v>
@@ -10343,7 +10441,7 @@
         <v>460</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F160" s="12" t="s">
         <v>473</v>
@@ -10386,7 +10484,7 @@
         <v>460</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F161" s="12" t="s">
         <v>473</v>
@@ -10429,7 +10527,7 @@
         <v>460</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F162" s="12" t="s">
         <v>476</v>
@@ -10472,7 +10570,7 @@
         <v>460</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F163" s="12" t="s">
         <v>476</v>
@@ -10515,7 +10613,7 @@
         <v>460</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F164" s="12" t="s">
         <v>479</v>
@@ -10558,7 +10656,7 @@
         <v>460</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F165" s="12" t="s">
         <v>479</v>
@@ -10601,7 +10699,7 @@
         <v>460</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>482</v>
@@ -10644,7 +10742,7 @@
         <v>460</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>482</v>
@@ -10687,7 +10785,7 @@
         <v>460</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>485</v>
@@ -10730,7 +10828,7 @@
         <v>460</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>485</v>
@@ -10773,7 +10871,7 @@
         <v>460</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>488</v>
@@ -10816,7 +10914,7 @@
         <v>460</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F171" s="12" t="s">
         <v>488</v>
@@ -10859,7 +10957,7 @@
         <v>460</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F172" s="12" t="s">
         <v>491</v>
@@ -10902,7 +11000,7 @@
         <v>460</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>491</v>
@@ -10945,7 +11043,7 @@
         <v>460</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F174" s="12" t="s">
         <v>495</v>
@@ -10988,7 +11086,7 @@
         <v>460</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F175" s="12" t="s">
         <v>495</v>
@@ -11031,7 +11129,7 @@
         <v>460</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F176" s="12" t="s">
         <v>498</v>
@@ -11074,7 +11172,7 @@
         <v>460</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F177" s="12" t="s">
         <v>498</v>
@@ -11117,7 +11215,7 @@
         <v>460</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F178" s="12" t="s">
         <v>501</v>
@@ -11158,7 +11256,7 @@
         <v>460</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F179" s="12" t="s">
         <v>505</v>
@@ -11201,7 +11299,7 @@
         <v>460</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F180" s="12" t="s">
         <v>505</v>
@@ -11244,7 +11342,7 @@
         <v>460</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F181" s="12" t="s">
         <v>508</v>
@@ -11285,7 +11383,7 @@
         <v>512</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F182" s="12" t="s">
         <v>513</v>
@@ -11326,7 +11424,7 @@
         <v>512</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F183" s="12" t="s">
         <v>516</v>
@@ -11458,7 +11556,7 @@
         <v>521</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>522</v>
@@ -11503,7 +11601,7 @@
         <v>521</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>524</v>
@@ -11550,7 +11648,7 @@
         <v>521</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>526</v>
@@ -11595,7 +11693,7 @@
         <v>521</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>528</v>
@@ -11640,7 +11738,7 @@
         <v>521</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>530</v>
@@ -11687,7 +11785,7 @@
         <v>521</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>532</v>
@@ -11732,7 +11830,7 @@
         <v>521</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>534</v>
@@ -11777,7 +11875,7 @@
         <v>521</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>536</v>
@@ -11822,7 +11920,7 @@
         <v>521</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>539</v>
@@ -11867,7 +11965,7 @@
         <v>521</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>541</v>
@@ -11912,7 +12010,7 @@
         <v>521</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>544</v>
@@ -11957,7 +12055,7 @@
         <v>521</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>546</v>
@@ -12002,7 +12100,7 @@
         <v>521</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>548</v>
@@ -12047,7 +12145,7 @@
         <v>552</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>553</v>
@@ -12092,7 +12190,7 @@
         <v>552</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>555</v>
@@ -12133,7 +12231,7 @@
         <v>552</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>557</v>
@@ -12174,7 +12272,7 @@
         <v>552</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>559</v>
@@ -12215,7 +12313,7 @@
         <v>552</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>561</v>
@@ -12256,7 +12354,7 @@
         <v>552</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>563</v>
@@ -12297,7 +12395,7 @@
         <v>552</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>565</v>
@@ -12338,7 +12436,7 @@
         <v>552</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>568</v>
@@ -12379,7 +12477,7 @@
         <v>552</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>570</v>
@@ -12420,7 +12518,7 @@
         <v>552</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>572</v>
@@ -12461,7 +12559,7 @@
         <v>552</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>575</v>
@@ -12506,7 +12604,7 @@
         <v>552</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>577</v>
@@ -12551,7 +12649,7 @@
         <v>552</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>579</v>
@@ -12592,7 +12690,7 @@
         <v>552</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>581</v>
@@ -12633,7 +12731,7 @@
         <v>552</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>583</v>
@@ -12674,7 +12772,7 @@
         <v>552</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>587</v>
@@ -12715,7 +12813,7 @@
         <v>552</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F31" s="15" t="s">
         <v>589</v>
@@ -12756,7 +12854,7 @@
         <v>552</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>591</v>
@@ -12797,7 +12895,7 @@
         <v>552</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>593</v>
@@ -12838,7 +12936,7 @@
         <v>552</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>595</v>
@@ -12879,7 +12977,7 @@
         <v>552</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>597</v>
@@ -12920,7 +13018,7 @@
         <v>552</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>599</v>
@@ -12961,7 +13059,7 @@
         <v>552</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>602</v>
@@ -13002,7 +13100,7 @@
         <v>552</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>604</v>
@@ -13043,7 +13141,7 @@
         <v>552</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>606</v>
@@ -13084,7 +13182,7 @@
         <v>552</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>610</v>
@@ -13125,7 +13223,7 @@
         <v>552</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>612</v>
@@ -13166,7 +13264,7 @@
         <v>552</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>614</v>
@@ -13207,7 +13305,7 @@
         <v>552</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F43" s="15" t="s">
         <v>616</v>
@@ -13248,7 +13346,7 @@
         <v>552</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>618</v>
@@ -13289,7 +13387,7 @@
         <v>552</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>621</v>
@@ -13330,7 +13428,7 @@
         <v>552</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>623</v>
@@ -13371,7 +13469,7 @@
         <v>552</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>626</v>
@@ -13412,7 +13510,7 @@
         <v>630</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>631</v>
@@ -13453,7 +13551,7 @@
         <v>630</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>633</v>
@@ -13494,7 +13592,7 @@
         <v>630</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>636</v>
@@ -13535,7 +13633,7 @@
         <v>630</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>638</v>
@@ -13576,7 +13674,7 @@
         <v>630</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>640</v>
@@ -13617,7 +13715,7 @@
         <v>630</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>642</v>
@@ -13658,7 +13756,7 @@
         <v>630</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>644</v>
@@ -13699,7 +13797,7 @@
         <v>630</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>646</v>
@@ -13740,7 +13838,7 @@
         <v>630</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>648</v>
@@ -13781,7 +13879,7 @@
         <v>630</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>651</v>
@@ -13822,7 +13920,7 @@
         <v>630</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>653</v>
@@ -13863,7 +13961,7 @@
         <v>630</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F59" s="15" t="s">
         <v>650</v>
@@ -13904,7 +14002,7 @@
         <v>630</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F60" s="15" t="s">
         <v>656</v>
@@ -13945,7 +14043,7 @@
         <v>630</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F61" s="15" t="s">
         <v>658</v>
@@ -13986,7 +14084,7 @@
         <v>630</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F62" s="15" t="s">
         <v>660</v>
@@ -14027,7 +14125,7 @@
         <v>630</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>663</v>
@@ -14068,7 +14166,7 @@
         <v>630</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>665</v>
@@ -14109,7 +14207,7 @@
         <v>630</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F65" s="15" t="s">
         <v>667</v>
@@ -14150,7 +14248,7 @@
         <v>671</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>672</v>
@@ -14195,7 +14293,7 @@
         <v>671</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F67" s="15" t="s">
         <v>674</v>
@@ -14240,7 +14338,7 @@
         <v>671</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F68" s="15" t="s">
         <v>676</v>
@@ -14285,7 +14383,7 @@
         <v>671</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F69" s="15" t="s">
         <v>678</v>
@@ -14332,7 +14430,7 @@
         <v>671</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F70" s="15" t="s">
         <v>678</v>
@@ -14379,7 +14477,7 @@
         <v>671</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>682</v>
@@ -14424,7 +14522,7 @@
         <v>671</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F72" s="15" t="s">
         <v>685</v>
@@ -14471,7 +14569,7 @@
         <v>671</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F73" s="15" t="s">
         <v>685</v>
@@ -14518,7 +14616,7 @@
         <v>671</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F74" s="15" t="s">
         <v>687</v>
@@ -14565,7 +14663,7 @@
         <v>671</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F75" s="15" t="s">
         <v>687</v>
@@ -14612,7 +14710,7 @@
         <v>671</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F76" s="15" t="s">
         <v>689</v>
@@ -14659,7 +14757,7 @@
         <v>671</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F77" s="15" t="s">
         <v>689</v>
@@ -14706,7 +14804,7 @@
         <v>671</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>691</v>
@@ -14753,7 +14851,7 @@
         <v>671</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F79" s="15" t="s">
         <v>691</v>
@@ -14800,7 +14898,7 @@
         <v>671</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F80" s="15" t="s">
         <v>693</v>
@@ -14847,7 +14945,7 @@
         <v>671</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F81" s="15" t="s">
         <v>693</v>
@@ -14894,7 +14992,7 @@
         <v>671</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F82" s="15" t="s">
         <v>695</v>
@@ -14941,7 +15039,7 @@
         <v>671</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F83" s="15" t="s">
         <v>695</v>
@@ -14988,7 +15086,7 @@
         <v>671</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F84" s="15" t="s">
         <v>698</v>
@@ -15033,7 +15131,7 @@
         <v>700</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>702</v>
@@ -15074,7 +15172,7 @@
         <v>700</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F86" s="15" t="s">
         <v>704</v>
@@ -15115,7 +15213,7 @@
         <v>700</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F87" s="15" t="s">
         <v>706</v>
@@ -15156,7 +15254,7 @@
         <v>700</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F88" s="15" t="s">
         <v>708</v>
@@ -15197,7 +15295,7 @@
         <v>700</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F89" s="15" t="s">
         <v>710</v>
@@ -15238,7 +15336,7 @@
         <v>700</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F90" s="15" t="s">
         <v>712</v>
@@ -15279,7 +15377,7 @@
         <v>700</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F91" s="15" t="s">
         <v>714</v>
@@ -15320,7 +15418,7 @@
         <v>718</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F92" s="15" t="s">
         <v>719</v>
@@ -15361,7 +15459,7 @@
         <v>718</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F93" s="15" t="s">
         <v>721</v>
@@ -15402,7 +15500,7 @@
         <v>718</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F94" s="15" t="s">
         <v>723</v>
@@ -15443,7 +15541,7 @@
         <v>718</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F95" s="15" t="s">
         <v>726</v>
@@ -15486,7 +15584,7 @@
         <v>718</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F96" s="15" t="s">
         <v>726</v>
@@ -15529,7 +15627,7 @@
         <v>718</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F97" s="15" t="s">
         <v>726</v>
@@ -15572,7 +15670,7 @@
         <v>718</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F98" s="15" t="s">
         <v>729</v>
@@ -15615,7 +15713,7 @@
         <v>718</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F99" s="15" t="s">
         <v>729</v>
@@ -15658,7 +15756,7 @@
         <v>718</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F100" s="15" t="s">
         <v>729</v>
@@ -15701,7 +15799,7 @@
         <v>718</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>731</v>
@@ -15744,7 +15842,7 @@
         <v>718</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F102" s="15" t="s">
         <v>731</v>
@@ -15787,7 +15885,7 @@
         <v>718</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F103" s="15" t="s">
         <v>731</v>
@@ -15830,7 +15928,7 @@
         <v>718</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F104" s="15" t="s">
         <v>733</v>
@@ -15873,7 +15971,7 @@
         <v>718</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F105" s="15" t="s">
         <v>733</v>
@@ -15916,7 +16014,7 @@
         <v>718</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>733</v>
@@ -15959,7 +16057,7 @@
         <v>718</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F107" s="15" t="s">
         <v>735</v>
@@ -16002,7 +16100,7 @@
         <v>718</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>735</v>
@@ -16045,7 +16143,7 @@
         <v>718</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>735</v>
@@ -16088,7 +16186,7 @@
         <v>718</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F110" s="15" t="s">
         <v>737</v>
@@ -16131,7 +16229,7 @@
         <v>718</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F111" s="15" t="s">
         <v>737</v>
@@ -16174,7 +16272,7 @@
         <v>718</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F112" s="15" t="s">
         <v>737</v>
@@ -16217,7 +16315,7 @@
         <v>718</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F113" s="15" t="s">
         <v>739</v>
@@ -16260,7 +16358,7 @@
         <v>718</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F114" s="15" t="s">
         <v>739</v>
@@ -16303,7 +16401,7 @@
         <v>718</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F115" s="15" t="s">
         <v>739</v>
@@ -16346,7 +16444,7 @@
         <v>718</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F116" s="15" t="s">
         <v>741</v>
@@ -16389,7 +16487,7 @@
         <v>718</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F117" s="15" t="s">
         <v>741</v>
@@ -16432,7 +16530,7 @@
         <v>718</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>741</v>
@@ -16475,7 +16573,7 @@
         <v>718</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>743</v>
@@ -16518,7 +16616,7 @@
         <v>718</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>743</v>
@@ -16561,7 +16659,7 @@
         <v>718</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F121" s="15" t="s">
         <v>743</v>
@@ -16604,7 +16702,7 @@
         <v>718</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F122" s="15" t="s">
         <v>745</v>
@@ -16647,7 +16745,7 @@
         <v>718</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F123" s="15" t="s">
         <v>745</v>
@@ -16690,7 +16788,7 @@
         <v>718</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F124" s="15" t="s">
         <v>745</v>
@@ -16733,7 +16831,7 @@
         <v>718</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F125" s="15" t="s">
         <v>747</v>
@@ -16776,7 +16874,7 @@
         <v>718</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F126" s="15" t="s">
         <v>747</v>
@@ -16819,7 +16917,7 @@
         <v>718</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F127" s="15" t="s">
         <v>747</v>
@@ -16862,7 +16960,7 @@
         <v>718</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F128" s="15" t="s">
         <v>749</v>
@@ -16905,7 +17003,7 @@
         <v>718</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F129" s="15" t="s">
         <v>749</v>
@@ -16948,7 +17046,7 @@
         <v>718</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F130" s="15" t="s">
         <v>749</v>
@@ -16991,7 +17089,7 @@
         <v>718</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F131" s="15" t="s">
         <v>751</v>
@@ -17034,7 +17132,7 @@
         <v>718</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F132" s="15" t="s">
         <v>751</v>
@@ -17077,7 +17175,7 @@
         <v>718</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F133" s="15" t="s">
         <v>751</v>
@@ -17120,7 +17218,7 @@
         <v>718</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F134" s="15" t="s">
         <v>754</v>
@@ -17163,7 +17261,7 @@
         <v>718</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F135" s="15" t="s">
         <v>754</v>
@@ -17206,7 +17304,7 @@
         <v>718</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F136" s="15" t="s">
         <v>754</v>
@@ -17249,7 +17347,7 @@
         <v>718</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F137" s="15" t="s">
         <v>756</v>
@@ -17292,7 +17390,7 @@
         <v>718</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F138" s="15" t="s">
         <v>756</v>
@@ -17335,7 +17433,7 @@
         <v>718</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F139" s="15" t="s">
         <v>756</v>
@@ -17378,7 +17476,7 @@
         <v>718</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F140" s="15" t="s">
         <v>758</v>
@@ -17421,7 +17519,7 @@
         <v>718</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F141" s="15" t="s">
         <v>758</v>
@@ -17464,7 +17562,7 @@
         <v>718</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F142" s="15" t="s">
         <v>758</v>
@@ -17507,7 +17605,7 @@
         <v>718</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F143" s="15" t="s">
         <v>761</v>
@@ -17550,7 +17648,7 @@
         <v>718</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F144" s="15" t="s">
         <v>761</v>
@@ -17593,7 +17691,7 @@
         <v>718</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F145" s="15" t="s">
         <v>761</v>
@@ -17636,7 +17734,7 @@
         <v>718</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F146" s="15" t="s">
         <v>763</v>
@@ -17679,7 +17777,7 @@
         <v>718</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F147" s="15" t="s">
         <v>763</v>
@@ -17722,7 +17820,7 @@
         <v>718</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F148" s="15" t="s">
         <v>763</v>
@@ -17765,7 +17863,7 @@
         <v>718</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F149" s="15" t="s">
         <v>765</v>
@@ -17808,7 +17906,7 @@
         <v>718</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>765</v>
@@ -17851,7 +17949,7 @@
         <v>718</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F151" s="15" t="s">
         <v>765</v>
@@ -17894,7 +17992,7 @@
         <v>769</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F152" s="15" t="s">
         <v>770</v>
@@ -17937,7 +18035,7 @@
         <v>769</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F153" s="15" t="s">
         <v>770</v>
@@ -17980,7 +18078,7 @@
         <v>769</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F154" s="15" t="s">
         <v>772</v>
@@ -18023,7 +18121,7 @@
         <v>769</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F155" s="15" t="s">
         <v>772</v>
@@ -18066,7 +18164,7 @@
         <v>769</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F156" s="15" t="s">
         <v>774</v>
@@ -18109,7 +18207,7 @@
         <v>769</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F157" s="15" t="s">
         <v>774</v>
@@ -18152,7 +18250,7 @@
         <v>769</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F158" s="15" t="s">
         <v>776</v>
@@ -18195,7 +18293,7 @@
         <v>769</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>776</v>
@@ -18238,7 +18336,7 @@
         <v>769</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>778</v>
@@ -18281,7 +18379,7 @@
         <v>769</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F161" s="15" t="s">
         <v>778</v>
@@ -18324,7 +18422,7 @@
         <v>769</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F162" s="15" t="s">
         <v>780</v>
@@ -18367,7 +18465,7 @@
         <v>769</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F163" s="15" t="s">
         <v>780</v>
@@ -18410,7 +18508,7 @@
         <v>769</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F164" s="15" t="s">
         <v>782</v>
@@ -18453,7 +18551,7 @@
         <v>769</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F165" s="15" t="s">
         <v>782</v>
@@ -18496,7 +18594,7 @@
         <v>769</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F166" s="15" t="s">
         <v>784</v>
@@ -18539,7 +18637,7 @@
         <v>769</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F167" s="15" t="s">
         <v>784</v>
@@ -18582,7 +18680,7 @@
         <v>769</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F168" s="15" t="s">
         <v>786</v>
@@ -18625,7 +18723,7 @@
         <v>769</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F169" s="15" t="s">
         <v>786</v>
@@ -18668,7 +18766,7 @@
         <v>769</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F170" s="15" t="s">
         <v>788</v>
@@ -18711,7 +18809,7 @@
         <v>769</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F171" s="15" t="s">
         <v>788</v>
@@ -18754,7 +18852,7 @@
         <v>769</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F172" s="15" t="s">
         <v>790</v>
@@ -18797,7 +18895,7 @@
         <v>769</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F173" s="15" t="s">
         <v>790</v>
@@ -18840,7 +18938,7 @@
         <v>769</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F174" s="15" t="s">
         <v>793</v>
@@ -18883,7 +18981,7 @@
         <v>769</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F175" s="15" t="s">
         <v>793</v>
@@ -18926,7 +19024,7 @@
         <v>769</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F176" s="15" t="s">
         <v>795</v>
@@ -18969,7 +19067,7 @@
         <v>769</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F177" s="15" t="s">
         <v>795</v>
@@ -19012,7 +19110,7 @@
         <v>769</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F178" s="15" t="s">
         <v>797</v>
@@ -19053,7 +19151,7 @@
         <v>769</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F179" s="15" t="s">
         <v>800</v>
@@ -19096,7 +19194,7 @@
         <v>769</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F180" s="15" t="s">
         <v>800</v>
@@ -19139,7 +19237,7 @@
         <v>769</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F181" s="15" t="s">
         <v>802</v>
@@ -19180,7 +19278,7 @@
         <v>805</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F182" s="15" t="s">
         <v>805</v>
@@ -19221,7 +19319,7 @@
         <v>805</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F183" s="15" t="s">
         <v>807</v>
@@ -20477,4 +20575,140 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F571AC4-D033-4191-BAD3-AC8F2AAF9EBB}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="24.26171875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.9453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7890625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.68359375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="27.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>830</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>831</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>835</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>838</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>846</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>849</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>850</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>843</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\new app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A89F2BE-9D8D-4ECE-B8A7-FC658821E381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D638AF89-EDE4-4E98-9A76-66498603A81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="859">
   <si>
     <t>Contact</t>
   </si>
@@ -1528,9 +1528,6 @@
     <t>ITM118</t>
   </si>
   <si>
-    <t>Desserts &amp; Fruit Plates</t>
-  </si>
-  <si>
     <t>Fruit Salad with Ice Cream</t>
   </si>
   <si>
@@ -1558,9 +1555,6 @@
     <t>ITM117</t>
   </si>
   <si>
-    <t>Mojitos &amp; Bottles</t>
-  </si>
-  <si>
     <t>Bottle Juice (1 Litre)</t>
   </si>
   <si>
@@ -2600,13 +2594,41 @@
   </si>
   <si>
     <t>Max File Size recommended</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM001.jpg
+/ItemImages</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM007.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg</t>
+  </si>
+  <si>
+    <t>Karak Tea 1</t>
+  </si>
+  <si>
+    <t>Karak Tea 3</t>
+  </si>
+  <si>
+    <t>Karak Tea 4</t>
+  </si>
+  <si>
+    <t>Karak Tea 5</t>
+  </si>
+  <si>
+    <t>Karak Tea 6</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2678,6 +2700,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2744,7 +2772,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2795,6 +2823,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3351,38 +3385,38 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D2" t="s">
         <v>122</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2" t="s">
+        <v>812</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="K2" t="s">
         <v>814</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="K2" t="s">
-        <v>816</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
       <c r="M2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3469,10 +3503,10 @@
         <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3486,7 +3520,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3500,7 +3534,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -3609,7 +3643,7 @@
         <v>121</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -3625,8 +3659,8 @@
       <c r="D2" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>821</v>
+      <c r="E2" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>134</v>
@@ -3646,11 +3680,11 @@
         <v>135</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="N2" s="12"/>
-      <c r="O2" s="12" t="s">
-        <v>71</v>
+      <c r="O2" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="11" t="b">
@@ -3670,8 +3704,8 @@
       <c r="D3" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>821</v>
+      <c r="E3" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>136</v>
@@ -3692,12 +3726,12 @@
       <c r="L3" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="19" t="s">
         <v>52</v>
       </c>
       <c r="N3" s="12"/>
-      <c r="O3" s="12" t="s">
-        <v>71</v>
+      <c r="O3" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="11" t="b">
@@ -3717,14 +3751,16 @@
       <c r="D4" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>821</v>
+      <c r="E4" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>138</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I4" s="11">
         <v>3</v>
       </c>
@@ -3738,11 +3774,11 @@
         <v>139</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N4" s="12"/>
-      <c r="O4" s="12" t="s">
-        <v>71</v>
+      <c r="O4" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P4" s="12"/>
       <c r="Q4" s="11" t="b">
@@ -3762,14 +3798,16 @@
       <c r="D5" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>821</v>
+      <c r="E5" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>140</v>
       </c>
       <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="H5" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I5" s="11">
         <v>4</v>
       </c>
@@ -3786,8 +3824,8 @@
         <v>73</v>
       </c>
       <c r="N5" s="12"/>
-      <c r="O5" s="12" t="s">
-        <v>71</v>
+      <c r="O5" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="b">
@@ -3807,8 +3845,8 @@
       <c r="D6" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>821</v>
+      <c r="E6" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>142</v>
@@ -3833,8 +3871,8 @@
         <v>55</v>
       </c>
       <c r="N6" s="12"/>
-      <c r="O6" s="12" t="s">
-        <v>71</v>
+      <c r="O6" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="11" t="b">
@@ -3854,14 +3892,16 @@
       <c r="D7" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>821</v>
+      <c r="E7" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>144</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="H7" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I7" s="11">
         <v>6</v>
       </c>
@@ -3878,8 +3918,8 @@
         <v>57</v>
       </c>
       <c r="N7" s="12"/>
-      <c r="O7" s="12" t="s">
-        <v>71</v>
+      <c r="O7" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="11" t="b">
@@ -3899,14 +3939,16 @@
       <c r="D8" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>821</v>
+      <c r="E8" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>146</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="H8" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I8" s="11">
         <v>7</v>
       </c>
@@ -3923,8 +3965,8 @@
         <v>56</v>
       </c>
       <c r="N8" s="12"/>
-      <c r="O8" s="12" t="s">
-        <v>71</v>
+      <c r="O8" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P8" s="12"/>
       <c r="Q8" s="11" t="b">
@@ -3947,14 +3989,16 @@
       <c r="D9" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>821</v>
+      <c r="E9" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>148</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="H9" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I9" s="11">
         <v>8</v>
       </c>
@@ -3971,8 +4015,8 @@
         <v>120</v>
       </c>
       <c r="N9" s="12"/>
-      <c r="O9" s="12" t="s">
-        <v>71</v>
+      <c r="O9" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P9" s="12"/>
       <c r="Q9" s="11" t="b">
@@ -3992,14 +4036,16 @@
       <c r="D10" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>821</v>
+      <c r="E10" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>151</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="H10" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I10" s="11">
         <v>1</v>
       </c>
@@ -4016,8 +4062,8 @@
         <v>56</v>
       </c>
       <c r="N10" s="12"/>
-      <c r="O10" s="12" t="s">
-        <v>71</v>
+      <c r="O10" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P10" s="12"/>
       <c r="Q10" s="11" t="b">
@@ -4037,14 +4083,16 @@
       <c r="D11" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>821</v>
+      <c r="E11" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>153</v>
       </c>
       <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="H11" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I11" s="11">
         <v>2</v>
       </c>
@@ -4061,8 +4109,8 @@
         <v>59</v>
       </c>
       <c r="N11" s="12"/>
-      <c r="O11" s="12" t="s">
-        <v>71</v>
+      <c r="O11" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="11" t="b">
@@ -4082,14 +4130,16 @@
       <c r="D12" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>821</v>
+      <c r="E12" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>156</v>
       </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="H12" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I12" s="11">
         <v>1</v>
       </c>
@@ -4106,8 +4156,8 @@
         <v>53</v>
       </c>
       <c r="N12" s="12"/>
-      <c r="O12" s="12" t="s">
-        <v>71</v>
+      <c r="O12" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P12" s="12"/>
       <c r="Q12" s="11" t="b">
@@ -4127,14 +4177,16 @@
       <c r="D13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>821</v>
+      <c r="E13" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>158</v>
       </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="H13" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I13" s="11">
         <v>2</v>
       </c>
@@ -4151,8 +4203,8 @@
         <v>58</v>
       </c>
       <c r="N13" s="12"/>
-      <c r="O13" s="12" t="s">
-        <v>71</v>
+      <c r="O13" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="11" t="b">
@@ -4172,14 +4224,16 @@
       <c r="D14" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>821</v>
+      <c r="E14" s="8" t="s">
+        <v>850</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>161</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I14" s="11">
         <v>1</v>
       </c>
@@ -4193,11 +4247,11 @@
         <v>162</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N14" s="12"/>
-      <c r="O14" s="12" t="s">
-        <v>71</v>
+      <c r="O14" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P14" s="12"/>
       <c r="Q14" s="11" t="b">
@@ -4218,13 +4272,15 @@
         <v>165</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>166</v>
       </c>
       <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="H15" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I15" s="11">
         <v>1</v>
       </c>
@@ -4241,8 +4297,8 @@
         <v>117</v>
       </c>
       <c r="N15" s="12"/>
-      <c r="O15" s="12" t="s">
-        <v>71</v>
+      <c r="O15" s="20" t="s">
+        <v>858</v>
       </c>
       <c r="P15" s="12"/>
       <c r="Q15" s="11" t="b">
@@ -4266,7 +4322,7 @@
         <v>165</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>169</v>
@@ -4307,7 +4363,7 @@
         <v>165</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>172</v>
@@ -4348,7 +4404,7 @@
         <v>165</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>175</v>
@@ -4389,7 +4445,7 @@
         <v>165</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>178</v>
@@ -4409,7 +4465,7 @@
         <v>179</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
@@ -4432,7 +4488,7 @@
         <v>165</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>181</v>
@@ -4473,7 +4529,7 @@
         <v>165</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>184</v>
@@ -4514,7 +4570,7 @@
         <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>188</v>
@@ -4555,7 +4611,7 @@
         <v>165</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>191</v>
@@ -4575,7 +4631,7 @@
         <v>192</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="12"/>
@@ -4601,7 +4657,7 @@
         <v>165</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>194</v>
@@ -4642,7 +4698,7 @@
         <v>165</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>197</v>
@@ -4687,7 +4743,7 @@
         <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>199</v>
@@ -4732,7 +4788,7 @@
         <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>202</v>
@@ -4773,7 +4829,7 @@
         <v>165</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>205</v>
@@ -4814,7 +4870,7 @@
         <v>165</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>208</v>
@@ -4855,7 +4911,7 @@
         <v>165</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>213</v>
@@ -4896,7 +4952,7 @@
         <v>165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>216</v>
@@ -4937,7 +4993,7 @@
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>219</v>
@@ -4978,7 +5034,7 @@
         <v>165</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>222</v>
@@ -5019,7 +5075,7 @@
         <v>165</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>225</v>
@@ -5060,7 +5116,7 @@
         <v>165</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>228</v>
@@ -5101,7 +5157,7 @@
         <v>165</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>231</v>
@@ -5142,7 +5198,7 @@
         <v>165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>235</v>
@@ -5183,7 +5239,7 @@
         <v>165</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>238</v>
@@ -5203,7 +5259,7 @@
         <v>239</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
@@ -5226,7 +5282,7 @@
         <v>165</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>241</v>
@@ -5267,7 +5323,7 @@
         <v>165</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>246</v>
@@ -5308,7 +5364,7 @@
         <v>165</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>249</v>
@@ -5349,7 +5405,7 @@
         <v>165</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>252</v>
@@ -5369,7 +5425,7 @@
         <v>253</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
@@ -5392,13 +5448,15 @@
         <v>165</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>255</v>
       </c>
       <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="H43" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I43" s="11">
         <v>4</v>
       </c>
@@ -5433,13 +5491,15 @@
         <v>165</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>197</v>
       </c>
       <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
+      <c r="H44" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I44" s="11">
         <v>5</v>
       </c>
@@ -5474,13 +5534,15 @@
         <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>261</v>
       </c>
       <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
+      <c r="H45" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I45" s="11">
         <v>1</v>
       </c>
@@ -5515,7 +5577,7 @@
         <v>165</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>264</v>
@@ -5556,7 +5618,7 @@
         <v>165</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>268</v>
@@ -5597,7 +5659,7 @@
         <v>273</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>274</v>
@@ -5638,7 +5700,7 @@
         <v>273</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>277</v>
@@ -5679,7 +5741,7 @@
         <v>273</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>281</v>
@@ -5723,7 +5785,7 @@
         <v>273</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>277</v>
@@ -5743,7 +5805,7 @@
         <v>284</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N51" s="12"/>
       <c r="O51" s="12"/>
@@ -5766,7 +5828,7 @@
         <v>273</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>286</v>
@@ -5807,7 +5869,7 @@
         <v>273</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>289</v>
@@ -5848,7 +5910,7 @@
         <v>273</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>292</v>
@@ -5889,7 +5951,7 @@
         <v>273</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>295</v>
@@ -5930,7 +5992,7 @@
         <v>273</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>298</v>
@@ -5971,7 +6033,7 @@
         <v>273</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>302</v>
@@ -6012,7 +6074,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>305</v>
@@ -6053,7 +6115,7 @@
         <v>273</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>308</v>
@@ -6094,7 +6156,7 @@
         <v>273</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>311</v>
@@ -6114,7 +6176,7 @@
         <v>312</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N60" s="12"/>
       <c r="O60" s="12"/>
@@ -6137,7 +6199,7 @@
         <v>273</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>314</v>
@@ -6178,7 +6240,7 @@
         <v>273</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>317</v>
@@ -6219,7 +6281,7 @@
         <v>273</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>321</v>
@@ -6260,7 +6322,7 @@
         <v>273</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>324</v>
@@ -6301,7 +6363,7 @@
         <v>273</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>327</v>
@@ -6342,7 +6404,7 @@
         <v>331</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>332</v>
@@ -6387,7 +6449,7 @@
         <v>331</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>334</v>
@@ -6432,7 +6494,7 @@
         <v>331</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>336</v>
@@ -6480,7 +6542,7 @@
         <v>331</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>338</v>
@@ -6527,7 +6589,7 @@
         <v>331</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>338</v>
@@ -6574,7 +6636,7 @@
         <v>331</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>342</v>
@@ -6619,7 +6681,7 @@
         <v>331</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>345</v>
@@ -6666,7 +6728,7 @@
         <v>331</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>345</v>
@@ -6674,7 +6736,9 @@
       <c r="G73" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I73" s="11">
         <v>1</v>
       </c>
@@ -6713,7 +6777,7 @@
         <v>331</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>347</v>
@@ -6721,7 +6785,9 @@
       <c r="G74" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="H74" s="11"/>
+      <c r="H74" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I74" s="11">
         <v>2</v>
       </c>
@@ -6760,7 +6826,7 @@
         <v>331</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>347</v>
@@ -6768,7 +6834,9 @@
       <c r="G75" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="H75" s="11"/>
+      <c r="H75" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I75" s="11">
         <v>2</v>
       </c>
@@ -6807,7 +6875,7 @@
         <v>331</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>349</v>
@@ -6854,7 +6922,7 @@
         <v>331</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>349</v>
@@ -6901,7 +6969,7 @@
         <v>331</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>351</v>
@@ -6948,7 +7016,7 @@
         <v>331</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>351</v>
@@ -6995,7 +7063,7 @@
         <v>331</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>353</v>
@@ -7042,7 +7110,7 @@
         <v>331</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>353</v>
@@ -7089,7 +7157,7 @@
         <v>331</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>355</v>
@@ -7136,7 +7204,7 @@
         <v>331</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>355</v>
@@ -7183,7 +7251,7 @@
         <v>331</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>358</v>
@@ -7228,7 +7296,7 @@
         <v>361</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>363</v>
@@ -7269,13 +7337,15 @@
         <v>361</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>366</v>
       </c>
       <c r="G86" s="11"/>
-      <c r="H86" s="11"/>
+      <c r="H86" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I86" s="11">
         <v>2</v>
       </c>
@@ -7310,13 +7380,15 @@
         <v>361</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>369</v>
       </c>
       <c r="G87" s="11"/>
-      <c r="H87" s="11"/>
+      <c r="H87" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I87" s="11">
         <v>3</v>
       </c>
@@ -7351,13 +7423,15 @@
         <v>361</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F88" s="12" t="s">
         <v>372</v>
       </c>
       <c r="G88" s="11"/>
-      <c r="H88" s="11"/>
+      <c r="H88" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I88" s="11">
         <v>4</v>
       </c>
@@ -7392,7 +7466,7 @@
         <v>361</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>375</v>
@@ -7433,7 +7507,7 @@
         <v>361</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F90" s="12" t="s">
         <v>379</v>
@@ -7474,7 +7548,7 @@
         <v>361</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>382</v>
@@ -7515,7 +7589,7 @@
         <v>387</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>388</v>
@@ -7556,7 +7630,7 @@
         <v>387</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>391</v>
@@ -7597,7 +7671,7 @@
         <v>387</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>394</v>
@@ -7638,7 +7712,7 @@
         <v>387</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>398</v>
@@ -7681,7 +7755,7 @@
         <v>387</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>398</v>
@@ -7724,7 +7798,7 @@
         <v>387</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>398</v>
@@ -7767,7 +7841,7 @@
         <v>387</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>402</v>
@@ -7810,7 +7884,7 @@
         <v>387</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>402</v>
@@ -7853,7 +7927,7 @@
         <v>387</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F100" s="12" t="s">
         <v>402</v>
@@ -7896,7 +7970,7 @@
         <v>387</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>405</v>
@@ -7939,7 +8013,7 @@
         <v>387</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>405</v>
@@ -7961,7 +8035,7 @@
         <v>406</v>
       </c>
       <c r="M102" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N102" s="12"/>
       <c r="O102" s="12"/>
@@ -7984,7 +8058,7 @@
         <v>387</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F103" s="12" t="s">
         <v>405</v>
@@ -8027,7 +8101,7 @@
         <v>387</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F104" s="12" t="s">
         <v>408</v>
@@ -8073,7 +8147,7 @@
         <v>387</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>408</v>
@@ -8116,7 +8190,7 @@
         <v>387</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>408</v>
@@ -8159,7 +8233,7 @@
         <v>387</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F107" s="12" t="s">
         <v>411</v>
@@ -8202,7 +8276,7 @@
         <v>387</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F108" s="12" t="s">
         <v>411</v>
@@ -8245,7 +8319,7 @@
         <v>387</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>411</v>
@@ -8288,7 +8362,7 @@
         <v>387</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F110" s="12" t="s">
         <v>414</v>
@@ -8331,7 +8405,7 @@
         <v>387</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>414</v>
@@ -8374,7 +8448,7 @@
         <v>387</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F112" s="12" t="s">
         <v>414</v>
@@ -8417,7 +8491,7 @@
         <v>387</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F113" s="12" t="s">
         <v>417</v>
@@ -8460,7 +8534,7 @@
         <v>387</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F114" s="12" t="s">
         <v>417</v>
@@ -8503,7 +8577,7 @@
         <v>387</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>417</v>
@@ -8546,7 +8620,7 @@
         <v>387</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F116" s="12" t="s">
         <v>420</v>
@@ -8589,7 +8663,7 @@
         <v>387</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F117" s="12" t="s">
         <v>420</v>
@@ -8632,7 +8706,7 @@
         <v>387</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F118" s="12" t="s">
         <v>420</v>
@@ -8675,7 +8749,7 @@
         <v>387</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>423</v>
@@ -8718,7 +8792,7 @@
         <v>387</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F120" s="12" t="s">
         <v>423</v>
@@ -8761,7 +8835,7 @@
         <v>387</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F121" s="12" t="s">
         <v>423</v>
@@ -8804,7 +8878,7 @@
         <v>387</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F122" s="12" t="s">
         <v>426</v>
@@ -8847,7 +8921,7 @@
         <v>387</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F123" s="12" t="s">
         <v>426</v>
@@ -8890,7 +8964,7 @@
         <v>387</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F124" s="12" t="s">
         <v>426</v>
@@ -8933,7 +9007,7 @@
         <v>387</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F125" s="12" t="s">
         <v>429</v>
@@ -8976,7 +9050,7 @@
         <v>387</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F126" s="12" t="s">
         <v>429</v>
@@ -9019,7 +9093,7 @@
         <v>387</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F127" s="12" t="s">
         <v>429</v>
@@ -9062,7 +9136,7 @@
         <v>387</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F128" s="12" t="s">
         <v>432</v>
@@ -9105,7 +9179,7 @@
         <v>387</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F129" s="12" t="s">
         <v>432</v>
@@ -9148,7 +9222,7 @@
         <v>387</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F130" s="12" t="s">
         <v>432</v>
@@ -9191,7 +9265,7 @@
         <v>387</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F131" s="12" t="s">
         <v>435</v>
@@ -9234,7 +9308,7 @@
         <v>387</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F132" s="12" t="s">
         <v>435</v>
@@ -9277,7 +9351,7 @@
         <v>387</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>435</v>
@@ -9320,7 +9394,7 @@
         <v>387</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F134" s="12" t="s">
         <v>439</v>
@@ -9363,7 +9437,7 @@
         <v>387</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F135" s="12" t="s">
         <v>439</v>
@@ -9406,7 +9480,7 @@
         <v>387</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F136" s="12" t="s">
         <v>439</v>
@@ -9449,7 +9523,7 @@
         <v>387</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F137" s="12" t="s">
         <v>442</v>
@@ -9492,7 +9566,7 @@
         <v>387</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F138" s="12" t="s">
         <v>442</v>
@@ -9535,7 +9609,7 @@
         <v>387</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F139" s="12" t="s">
         <v>442</v>
@@ -9578,7 +9652,7 @@
         <v>387</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F140" s="12" t="s">
         <v>445</v>
@@ -9621,7 +9695,7 @@
         <v>387</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F141" s="12" t="s">
         <v>445</v>
@@ -9664,7 +9738,7 @@
         <v>387</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F142" s="12" t="s">
         <v>445</v>
@@ -9707,7 +9781,7 @@
         <v>387</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F143" s="12" t="s">
         <v>449</v>
@@ -9750,7 +9824,7 @@
         <v>387</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F144" s="12" t="s">
         <v>449</v>
@@ -9793,7 +9867,7 @@
         <v>387</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>449</v>
@@ -9836,7 +9910,7 @@
         <v>387</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F146" s="12" t="s">
         <v>452</v>
@@ -9879,7 +9953,7 @@
         <v>387</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>452</v>
@@ -9915,14 +9989,14 @@
       <c r="B148" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C148" s="12" t="s">
-        <v>448</v>
+      <c r="C148" s="19" t="s">
+        <v>857</v>
       </c>
       <c r="D148" s="12" t="s">
         <v>387</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>452</v>
@@ -9958,14 +10032,14 @@
       <c r="B149" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C149" s="12" t="s">
-        <v>448</v>
+      <c r="C149" s="19" t="s">
+        <v>857</v>
       </c>
       <c r="D149" s="12" t="s">
         <v>387</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>455</v>
@@ -10001,14 +10075,14 @@
       <c r="B150" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C150" s="12" t="s">
-        <v>448</v>
+      <c r="C150" s="19" t="s">
+        <v>857</v>
       </c>
       <c r="D150" s="12" t="s">
         <v>387</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>455</v>
@@ -10044,14 +10118,14 @@
       <c r="B151" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C151" s="12" t="s">
-        <v>448</v>
+      <c r="C151" s="19" t="s">
+        <v>857</v>
       </c>
       <c r="D151" s="12" t="s">
         <v>387</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>455</v>
@@ -10094,7 +10168,7 @@
         <v>460</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F152" s="12" t="s">
         <v>461</v>
@@ -10137,7 +10211,7 @@
         <v>460</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>461</v>
@@ -10183,7 +10257,7 @@
         <v>460</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>464</v>
@@ -10226,7 +10300,7 @@
         <v>460</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F155" s="12" t="s">
         <v>464</v>
@@ -10262,14 +10336,14 @@
       <c r="B156" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C156" s="12" t="s">
-        <v>459</v>
+      <c r="C156" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D156" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>467</v>
@@ -10305,14 +10379,14 @@
       <c r="B157" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C157" s="12" t="s">
-        <v>459</v>
+      <c r="C157" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D157" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>467</v>
@@ -10348,14 +10422,14 @@
       <c r="B158" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C158" s="12" t="s">
-        <v>459</v>
+      <c r="C158" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D158" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F158" s="12" t="s">
         <v>470</v>
@@ -10391,14 +10465,14 @@
       <c r="B159" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C159" s="12" t="s">
-        <v>459</v>
+      <c r="C159" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D159" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F159" s="12" t="s">
         <v>470</v>
@@ -10434,14 +10508,14 @@
       <c r="B160" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C160" s="12" t="s">
-        <v>459</v>
+      <c r="C160" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D160" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F160" s="12" t="s">
         <v>473</v>
@@ -10477,14 +10551,14 @@
       <c r="B161" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C161" s="12" t="s">
-        <v>459</v>
+      <c r="C161" s="19" t="s">
+        <v>856</v>
       </c>
       <c r="D161" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F161" s="12" t="s">
         <v>473</v>
@@ -10520,14 +10594,14 @@
       <c r="B162" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C162" s="12" t="s">
-        <v>459</v>
+      <c r="C162" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D162" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F162" s="12" t="s">
         <v>476</v>
@@ -10563,14 +10637,14 @@
       <c r="B163" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C163" s="12" t="s">
-        <v>459</v>
+      <c r="C163" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D163" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F163" s="12" t="s">
         <v>476</v>
@@ -10606,14 +10680,14 @@
       <c r="B164" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C164" s="12" t="s">
-        <v>459</v>
+      <c r="C164" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D164" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F164" s="12" t="s">
         <v>479</v>
@@ -10649,14 +10723,14 @@
       <c r="B165" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C165" s="12" t="s">
-        <v>459</v>
+      <c r="C165" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F165" s="12" t="s">
         <v>479</v>
@@ -10692,14 +10766,14 @@
       <c r="B166" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C166" s="12" t="s">
-        <v>459</v>
+      <c r="C166" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>482</v>
@@ -10735,14 +10809,14 @@
       <c r="B167" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C167" s="12" t="s">
-        <v>459</v>
+      <c r="C167" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D167" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>482</v>
@@ -10778,14 +10852,14 @@
       <c r="B168" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C168" s="12" t="s">
-        <v>459</v>
+      <c r="C168" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D168" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>485</v>
@@ -10821,14 +10895,14 @@
       <c r="B169" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C169" s="12" t="s">
-        <v>459</v>
+      <c r="C169" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D169" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>485</v>
@@ -10864,14 +10938,14 @@
       <c r="B170" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C170" s="12" t="s">
-        <v>459</v>
+      <c r="C170" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D170" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>488</v>
@@ -10907,14 +10981,14 @@
       <c r="B171" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C171" s="12" t="s">
-        <v>459</v>
+      <c r="C171" s="19" t="s">
+        <v>855</v>
       </c>
       <c r="D171" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F171" s="12" t="s">
         <v>488</v>
@@ -10950,14 +11024,14 @@
       <c r="B172" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C172" s="12" t="s">
-        <v>459</v>
+      <c r="C172" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D172" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F172" s="12" t="s">
         <v>491</v>
@@ -10993,14 +11067,14 @@
       <c r="B173" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C173" s="12" t="s">
-        <v>459</v>
+      <c r="C173" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D173" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>491</v>
@@ -11036,17 +11110,17 @@
       <c r="B174" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C174" s="12" t="s">
-        <v>494</v>
+      <c r="C174" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D174" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G174" s="11" t="s">
         <v>339</v>
@@ -11062,7 +11136,7 @@
         <v>10</v>
       </c>
       <c r="L174" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M174" s="12"/>
       <c r="N174" s="12"/>
@@ -11079,17 +11153,17 @@
       <c r="B175" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C175" s="12" t="s">
-        <v>494</v>
+      <c r="C175" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D175" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F175" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G175" s="11" t="s">
         <v>341</v>
@@ -11105,7 +11179,7 @@
         <v>12</v>
       </c>
       <c r="L175" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -11117,22 +11191,22 @@
     </row>
     <row r="176" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C176" s="12" t="s">
-        <v>494</v>
+      <c r="C176" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D176" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F176" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G176" s="11" t="s">
         <v>339</v>
@@ -11148,7 +11222,7 @@
         <v>5</v>
       </c>
       <c r="L176" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M176" s="12"/>
       <c r="N176" s="12"/>
@@ -11160,22 +11234,22 @@
     </row>
     <row r="177" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C177" s="12" t="s">
-        <v>494</v>
+      <c r="C177" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D177" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F177" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G177" s="11" t="s">
         <v>341</v>
@@ -11191,7 +11265,7 @@
         <v>10</v>
       </c>
       <c r="L177" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M177" s="12"/>
       <c r="N177" s="12"/>
@@ -11203,22 +11277,22 @@
     </row>
     <row r="178" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C178" s="12" t="s">
-        <v>494</v>
+      <c r="C178" s="19" t="s">
+        <v>854</v>
       </c>
       <c r="D178" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
@@ -11232,7 +11306,7 @@
         <v>12</v>
       </c>
       <c r="L178" s="14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M178" s="12"/>
       <c r="N178" s="12"/>
@@ -11244,22 +11318,22 @@
     </row>
     <row r="179" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C179" s="12" t="s">
-        <v>504</v>
+      <c r="C179" s="19" t="s">
+        <v>853</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G179" s="11" t="s">
         <v>339</v>
@@ -11275,7 +11349,7 @@
         <v>25</v>
       </c>
       <c r="L179" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M179" s="12"/>
       <c r="N179" s="12"/>
@@ -11287,22 +11361,22 @@
     </row>
     <row r="180" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C180" s="12" t="s">
-        <v>504</v>
+      <c r="C180" s="19" t="s">
+        <v>853</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>341</v>
@@ -11318,7 +11392,7 @@
         <v>30</v>
       </c>
       <c r="L180" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M180" s="12"/>
       <c r="N180" s="12"/>
@@ -11330,22 +11404,22 @@
     </row>
     <row r="181" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C181" s="12" t="s">
-        <v>504</v>
+      <c r="C181" s="19" t="s">
+        <v>853</v>
       </c>
       <c r="D181" s="12" t="s">
         <v>460</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F181" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
@@ -11359,7 +11433,7 @@
         <v>10</v>
       </c>
       <c r="L181" s="14" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M181" s="12"/>
       <c r="N181" s="12"/>
@@ -11371,22 +11445,22 @@
     </row>
     <row r="182" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C182" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="B182" s="12" t="s">
+      <c r="D182" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F182" s="12" t="s">
         <v>511</v>
-      </c>
-      <c r="C182" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="D182" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F182" s="12" t="s">
-        <v>513</v>
       </c>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
@@ -11400,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M182" s="12"/>
       <c r="N182" s="12"/>
@@ -11412,22 +11486,22 @@
     </row>
     <row r="183" spans="1:17" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
@@ -11441,10 +11515,10 @@
         <v>4</v>
       </c>
       <c r="L183" s="14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M183" s="12" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N183" s="12"/>
       <c r="O183" s="12"/>
@@ -11461,8 +11535,16 @@
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://raw.githubusercontent.com/DigiDatas/KARAK-WA-KARAK/main/logo.png" xr:uid="{8DE9E557-F3B0-434E-98AC-B26B26771AD6}"/>
-    <hyperlink ref="E3:E183" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/KARAK-WA-KARAK/main/logo.png" xr:uid="{3B1431E2-20FA-4502-A7BB-EC59616F0024}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{8DE9E557-F3B0-434E-98AC-B26B26771AD6}"/>
+    <hyperlink ref="E3:E14" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM001.jpg_x000a_/ItemImages" xr:uid="{DD02AF20-9319-4EFF-888A-177906FC7290}"/>
+    <hyperlink ref="E15" r:id="rId3" xr:uid="{4D05D8FA-37AC-4FE4-A4B6-56782248FA97}"/>
+    <hyperlink ref="E16:E47" r:id="rId4" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM007.jpg" xr:uid="{39724CD9-AE3A-4BCE-99F4-A1A3845A2CB7}"/>
+    <hyperlink ref="E48" r:id="rId5" xr:uid="{3F243788-E863-45B9-815B-BAFC290A401E}"/>
+    <hyperlink ref="E49:E65" r:id="rId6" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg" xr:uid="{84C1ACAE-469E-4E4B-A0FF-2358629AD8EB}"/>
+    <hyperlink ref="E66" r:id="rId7" xr:uid="{E2559F05-4803-4BA3-B273-A550232E8854}"/>
+    <hyperlink ref="E67:E84" r:id="rId8" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg" xr:uid="{1342928F-E905-4149-B20A-08B975EABE45}"/>
+    <hyperlink ref="O2" r:id="rId9" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{D2746854-1D7F-4CD4-91B9-FA32C9E32A74}"/>
+    <hyperlink ref="O3:O15" r:id="rId10" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{C8CECB9D-E2EF-49B9-ADDC-D699A1C77B63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11506,7 +11588,7 @@
         <v>126</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>128</v>
@@ -11547,19 +11629,19 @@
         <v>28</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>520</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>522</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="11"/>
@@ -11573,7 +11655,7 @@
         <v>15</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>52</v>
@@ -11592,19 +11674,19 @@
         <v>29</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="11" t="s">
@@ -11620,7 +11702,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>52</v>
@@ -11639,19 +11721,19 @@
         <v>31</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="11"/>
@@ -11665,7 +11747,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>54</v>
@@ -11684,19 +11766,19 @@
         <v>32</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="11"/>
@@ -11710,7 +11792,7 @@
         <v>15</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M5" s="12" t="s">
         <v>73</v>
@@ -11729,19 +11811,19 @@
         <v>33</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="11" t="s">
@@ -11757,7 +11839,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>55</v>
@@ -11776,19 +11858,19 @@
         <v>34</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="11"/>
@@ -11802,7 +11884,7 @@
         <v>7</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>57</v>
@@ -11821,19 +11903,19 @@
         <v>36</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="11"/>
@@ -11847,7 +11929,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>56</v>
@@ -11866,19 +11948,19 @@
         <v>37</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="11"/>
@@ -11892,7 +11974,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="M9" s="12" t="s">
         <v>120</v>
@@ -11911,19 +11993,19 @@
         <v>35</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="11"/>
@@ -11937,7 +12019,7 @@
         <v>12</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>56</v>
@@ -11956,19 +12038,19 @@
         <v>39</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="11"/>
@@ -11982,7 +12064,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M11" s="12" t="s">
         <v>59</v>
@@ -12001,19 +12083,19 @@
         <v>30</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="11"/>
@@ -12027,7 +12109,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>53</v>
@@ -12046,19 +12128,19 @@
         <v>38</v>
       </c>
       <c r="B13" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="11"/>
@@ -12072,7 +12154,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M13" s="12" t="s">
         <v>58</v>
@@ -12091,19 +12173,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>548</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>521</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="11"/>
@@ -12117,7 +12199,7 @@
         <v>8</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M14" s="12" t="s">
         <v>60</v>
@@ -12136,19 +12218,19 @@
         <v>105</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="E15" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>551</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>552</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>553</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="11"/>
@@ -12162,7 +12244,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="M15" s="12" t="s">
         <v>117</v>
@@ -12181,19 +12263,19 @@
         <v>168</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="11"/>
@@ -12207,7 +12289,7 @@
         <v>8</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
@@ -12222,19 +12304,19 @@
         <v>171</v>
       </c>
       <c r="B17" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="11"/>
@@ -12248,7 +12330,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -12263,19 +12345,19 @@
         <v>174</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="11"/>
@@ -12289,7 +12371,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -12304,19 +12386,19 @@
         <v>177</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="11"/>
@@ -12330,7 +12412,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -12345,19 +12427,19 @@
         <v>180</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="11"/>
@@ -12371,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -12386,19 +12468,19 @@
         <v>183</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="11"/>
@@ -12412,7 +12494,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -12427,19 +12509,19 @@
         <v>186</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="11"/>
@@ -12453,7 +12535,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -12468,19 +12550,19 @@
         <v>190</v>
       </c>
       <c r="B23" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="11"/>
@@ -12494,7 +12576,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -12509,19 +12591,19 @@
         <v>193</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="11"/>
@@ -12535,7 +12617,7 @@
         <v>12</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -12550,19 +12632,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="11"/>
@@ -12576,7 +12658,7 @@
         <v>8</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>118</v>
@@ -12595,19 +12677,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="11"/>
@@ -12621,7 +12703,7 @@
         <v>20</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>119</v>
@@ -12640,19 +12722,19 @@
         <v>201</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="11"/>
@@ -12666,7 +12748,7 @@
         <v>5</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
@@ -12681,19 +12763,19 @@
         <v>204</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="11"/>
@@ -12707,7 +12789,7 @@
         <v>13</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
@@ -12722,19 +12804,19 @@
         <v>207</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>552</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="11"/>
@@ -12748,7 +12830,7 @@
         <v>7</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
@@ -12763,19 +12845,19 @@
         <v>210</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>585</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>552</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="11"/>
@@ -12789,7 +12871,7 @@
         <v>12</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
@@ -12804,19 +12886,19 @@
         <v>215</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="11"/>
@@ -12830,7 +12912,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
@@ -12845,19 +12927,19 @@
         <v>218</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="11"/>
@@ -12871,7 +12953,7 @@
         <v>9</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
@@ -12886,19 +12968,19 @@
         <v>221</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="11"/>
@@ -12912,7 +12994,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
@@ -12927,19 +13009,19 @@
         <v>224</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="11"/>
@@ -12953,7 +13035,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
@@ -12968,19 +13050,19 @@
         <v>227</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="11"/>
@@ -12994,7 +13076,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
@@ -13009,19 +13091,19 @@
         <v>230</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G36" s="15"/>
       <c r="H36" s="11"/>
@@ -13035,7 +13117,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
@@ -13050,19 +13132,19 @@
         <v>233</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="11"/>
@@ -13076,7 +13158,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
@@ -13091,19 +13173,19 @@
         <v>237</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G38" s="15"/>
       <c r="H38" s="11"/>
@@ -13117,7 +13199,7 @@
         <v>12</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
@@ -13132,19 +13214,19 @@
         <v>240</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G39" s="15"/>
       <c r="H39" s="11"/>
@@ -13158,7 +13240,7 @@
         <v>12</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
@@ -13173,19 +13255,19 @@
         <v>243</v>
       </c>
       <c r="B40" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F40" s="15" t="s">
         <v>608</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>609</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>552</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>610</v>
       </c>
       <c r="G40" s="15"/>
       <c r="H40" s="11"/>
@@ -13199,7 +13281,7 @@
         <v>5</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
@@ -13214,19 +13296,19 @@
         <v>248</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G41" s="15"/>
       <c r="H41" s="11"/>
@@ -13240,7 +13322,7 @@
         <v>5</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
@@ -13255,19 +13337,19 @@
         <v>251</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G42" s="15"/>
       <c r="H42" s="11"/>
@@ -13281,7 +13363,7 @@
         <v>4</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
@@ -13296,19 +13378,19 @@
         <v>254</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G43" s="15"/>
       <c r="H43" s="11"/>
@@ -13322,7 +13404,7 @@
         <v>4</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
@@ -13337,19 +13419,19 @@
         <v>257</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G44" s="15"/>
       <c r="H44" s="11"/>
@@ -13363,7 +13445,7 @@
         <v>5</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
@@ -13378,19 +13460,19 @@
         <v>259</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G45" s="15"/>
       <c r="H45" s="11"/>
@@ -13404,7 +13486,7 @@
         <v>3</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
@@ -13419,19 +13501,19 @@
         <v>263</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="11"/>
@@ -13445,7 +13527,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M46" s="12"/>
       <c r="N46" s="12"/>
@@ -13460,19 +13542,19 @@
         <v>266</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="11"/>
@@ -13486,7 +13568,7 @@
         <v>3</v>
       </c>
       <c r="L47" s="16" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
@@ -13501,19 +13583,19 @@
         <v>270</v>
       </c>
       <c r="B48" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="D48" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="E48" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F48" s="15" t="s">
         <v>629</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>631</v>
       </c>
       <c r="G48" s="15"/>
       <c r="H48" s="11"/>
@@ -13527,7 +13609,7 @@
         <v>60</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
@@ -13542,19 +13624,19 @@
         <v>276</v>
       </c>
       <c r="B49" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="D49" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="11"/>
@@ -13568,7 +13650,7 @@
         <v>50</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
@@ -13583,19 +13665,19 @@
         <v>279</v>
       </c>
       <c r="B50" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D50" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G50" s="15"/>
       <c r="H50" s="11"/>
@@ -13609,7 +13691,7 @@
         <v>22</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
@@ -13624,19 +13706,19 @@
         <v>283</v>
       </c>
       <c r="B51" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D51" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C51" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E51" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="11"/>
@@ -13650,7 +13732,7 @@
         <v>13</v>
       </c>
       <c r="L51" s="16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
@@ -13665,19 +13747,19 @@
         <v>285</v>
       </c>
       <c r="B52" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D52" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C52" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E52" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G52" s="15"/>
       <c r="H52" s="11"/>
@@ -13691,7 +13773,7 @@
         <v>12</v>
       </c>
       <c r="L52" s="16" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M52" s="12"/>
       <c r="N52" s="12"/>
@@ -13706,19 +13788,19 @@
         <v>288</v>
       </c>
       <c r="B53" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C53" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="11"/>
@@ -13732,7 +13814,7 @@
         <v>12</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
@@ -13747,19 +13829,19 @@
         <v>291</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D54" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C54" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E54" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G54" s="15"/>
       <c r="H54" s="11"/>
@@ -13773,7 +13855,7 @@
         <v>12</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
@@ -13788,19 +13870,19 @@
         <v>294</v>
       </c>
       <c r="B55" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D55" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E55" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G55" s="15"/>
       <c r="H55" s="11"/>
@@ -13814,7 +13896,7 @@
         <v>12</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M55" s="12"/>
       <c r="N55" s="12"/>
@@ -13829,19 +13911,19 @@
         <v>297</v>
       </c>
       <c r="B56" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D56" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E56" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="11"/>
@@ -13855,7 +13937,7 @@
         <v>12</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M56" s="12"/>
       <c r="N56" s="12"/>
@@ -13870,19 +13952,19 @@
         <v>300</v>
       </c>
       <c r="B57" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D57" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C57" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E57" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G57" s="15"/>
       <c r="H57" s="11"/>
@@ -13896,7 +13978,7 @@
         <v>12</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M57" s="12"/>
       <c r="N57" s="12"/>
@@ -13911,19 +13993,19 @@
         <v>304</v>
       </c>
       <c r="B58" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C58" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E58" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="11"/>
@@ -13937,7 +14019,7 @@
         <v>16</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="M58" s="12"/>
       <c r="N58" s="12"/>
@@ -13952,19 +14034,19 @@
         <v>307</v>
       </c>
       <c r="B59" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E59" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="11"/>
@@ -13978,7 +14060,7 @@
         <v>12</v>
       </c>
       <c r="L59" s="16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
@@ -13993,19 +14075,19 @@
         <v>310</v>
       </c>
       <c r="B60" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C60" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="11"/>
@@ -14019,7 +14101,7 @@
         <v>12</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
@@ -14034,19 +14116,19 @@
         <v>313</v>
       </c>
       <c r="B61" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D61" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E61" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G61" s="15"/>
       <c r="H61" s="11"/>
@@ -14060,7 +14142,7 @@
         <v>24</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
@@ -14075,19 +14157,19 @@
         <v>316</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G62" s="15"/>
       <c r="H62" s="11"/>
@@ -14101,7 +14183,7 @@
         <v>10</v>
       </c>
       <c r="L62" s="16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
@@ -14116,19 +14198,19 @@
         <v>319</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="D63" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C63" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E63" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G63" s="15"/>
       <c r="H63" s="11"/>
@@ -14142,7 +14224,7 @@
         <v>10</v>
       </c>
       <c r="L63" s="16" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
@@ -14157,19 +14239,19 @@
         <v>323</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="D64" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C64" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G64" s="15"/>
       <c r="H64" s="11"/>
@@ -14183,7 +14265,7 @@
         <v>12</v>
       </c>
       <c r="L64" s="16" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="M64" s="12"/>
       <c r="N64" s="12"/>
@@ -14198,19 +14280,19 @@
         <v>326</v>
       </c>
       <c r="B65" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="D65" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>630</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G65" s="15"/>
       <c r="H65" s="11"/>
@@ -14224,7 +14306,7 @@
         <v>12</v>
       </c>
       <c r="L65" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
@@ -14239,19 +14321,19 @@
         <v>45</v>
       </c>
       <c r="B66" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D66" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="E66" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F66" s="15" t="s">
         <v>670</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>671</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>672</v>
       </c>
       <c r="G66" s="15"/>
       <c r="H66" s="11"/>
@@ -14265,7 +14347,7 @@
         <v>12</v>
       </c>
       <c r="L66" s="16" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="M66" s="12" t="s">
         <v>63</v>
@@ -14284,19 +14366,19 @@
         <v>98</v>
       </c>
       <c r="B67" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D67" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E67" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G67" s="15"/>
       <c r="H67" s="11"/>
@@ -14310,7 +14392,7 @@
         <v>18</v>
       </c>
       <c r="L67" s="16" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="M67" s="12" t="s">
         <v>110</v>
@@ -14329,19 +14411,19 @@
         <v>101</v>
       </c>
       <c r="B68" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D68" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G68" s="15"/>
       <c r="H68" s="11"/>
@@ -14355,7 +14437,7 @@
         <v>15</v>
       </c>
       <c r="L68" s="16" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="M68" s="12" t="s">
         <v>113</v>
@@ -14374,22 +14456,22 @@
         <v>103</v>
       </c>
       <c r="B69" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D69" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H69" s="11"/>
       <c r="I69" s="11">
@@ -14402,7 +14484,7 @@
         <v>8</v>
       </c>
       <c r="L69" s="16" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M69" s="12" t="s">
         <v>114</v>
@@ -14421,22 +14503,22 @@
         <v>103</v>
       </c>
       <c r="B70" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E70" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H70" s="11"/>
       <c r="I70" s="11">
@@ -14449,7 +14531,7 @@
         <v>15</v>
       </c>
       <c r="L70" s="16" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M70" s="12" t="s">
         <v>114</v>
@@ -14468,19 +14550,19 @@
         <v>104</v>
       </c>
       <c r="B71" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D71" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C71" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="11"/>
@@ -14494,7 +14576,7 @@
         <v>15</v>
       </c>
       <c r="L71" s="16" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M71" s="12" t="s">
         <v>116</v>
@@ -14513,22 +14595,22 @@
         <v>41</v>
       </c>
       <c r="B72" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D72" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H72" s="11"/>
       <c r="I72" s="11">
@@ -14541,7 +14623,7 @@
         <v>5</v>
       </c>
       <c r="L72" s="16" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M72" s="12" t="s">
         <v>109</v>
@@ -14560,22 +14642,22 @@
         <v>41</v>
       </c>
       <c r="B73" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D73" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H73" s="11"/>
       <c r="I73" s="11">
@@ -14588,7 +14670,7 @@
         <v>10</v>
       </c>
       <c r="L73" s="16" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M73" s="12" t="s">
         <v>109</v>
@@ -14607,22 +14689,22 @@
         <v>42</v>
       </c>
       <c r="B74" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D74" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H74" s="11"/>
       <c r="I74" s="11">
@@ -14635,7 +14717,7 @@
         <v>5</v>
       </c>
       <c r="L74" s="16" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M74" s="12" t="s">
         <v>61</v>
@@ -14654,22 +14736,22 @@
         <v>42</v>
       </c>
       <c r="B75" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D75" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C75" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H75" s="11"/>
       <c r="I75" s="11">
@@ -14682,7 +14764,7 @@
         <v>10</v>
       </c>
       <c r="L75" s="16" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M75" s="12" t="s">
         <v>61</v>
@@ -14701,22 +14783,22 @@
         <v>43</v>
       </c>
       <c r="B76" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D76" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C76" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E76" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H76" s="11"/>
       <c r="I76" s="11">
@@ -14729,7 +14811,7 @@
         <v>5</v>
       </c>
       <c r="L76" s="16" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M76" s="12" t="s">
         <v>61</v>
@@ -14748,22 +14830,22 @@
         <v>43</v>
       </c>
       <c r="B77" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D77" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C77" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E77" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H77" s="11"/>
       <c r="I77" s="11">
@@ -14776,7 +14858,7 @@
         <v>10</v>
       </c>
       <c r="L77" s="16" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M77" s="12" t="s">
         <v>61</v>
@@ -14795,22 +14877,22 @@
         <v>44</v>
       </c>
       <c r="B78" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D78" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E78" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H78" s="11"/>
       <c r="I78" s="11">
@@ -14823,7 +14905,7 @@
         <v>5</v>
       </c>
       <c r="L78" s="16" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="M78" s="12" t="s">
         <v>62</v>
@@ -14842,22 +14924,22 @@
         <v>44</v>
       </c>
       <c r="B79" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D79" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C79" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H79" s="11"/>
       <c r="I79" s="11">
@@ -14870,7 +14952,7 @@
         <v>10</v>
       </c>
       <c r="L79" s="16" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="M79" s="12" t="s">
         <v>62</v>
@@ -14889,22 +14971,22 @@
         <v>99</v>
       </c>
       <c r="B80" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D80" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C80" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E80" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H80" s="11"/>
       <c r="I80" s="11">
@@ -14917,7 +14999,7 @@
         <v>5</v>
       </c>
       <c r="L80" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="M80" s="12" t="s">
         <v>111</v>
@@ -14936,22 +15018,22 @@
         <v>99</v>
       </c>
       <c r="B81" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D81" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C81" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E81" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H81" s="11"/>
       <c r="I81" s="11">
@@ -14964,7 +15046,7 @@
         <v>10</v>
       </c>
       <c r="L81" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="M81" s="12" t="s">
         <v>111</v>
@@ -14983,22 +15065,22 @@
         <v>102</v>
       </c>
       <c r="B82" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D82" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C82" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E82" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H82" s="11"/>
       <c r="I82" s="11">
@@ -15011,7 +15093,7 @@
         <v>5</v>
       </c>
       <c r="L82" s="16" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M82" s="12" t="s">
         <v>115</v>
@@ -15030,22 +15112,22 @@
         <v>102</v>
       </c>
       <c r="B83" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D83" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>684</v>
-      </c>
-      <c r="D83" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E83" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H83" s="11"/>
       <c r="I83" s="11">
@@ -15058,7 +15140,7 @@
         <v>10</v>
       </c>
       <c r="L83" s="16" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M83" s="12" t="s">
         <v>115</v>
@@ -15077,19 +15159,19 @@
         <v>100</v>
       </c>
       <c r="B84" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="D84" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C84" s="15" t="s">
-        <v>697</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>671</v>
-      </c>
       <c r="E84" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G84" s="15"/>
       <c r="H84" s="11"/>
@@ -15103,7 +15185,7 @@
         <v>18</v>
       </c>
       <c r="L84" s="16" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M84" s="12" t="s">
         <v>112</v>
@@ -15122,19 +15204,19 @@
         <v>360</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F85" s="15" t="s">
         <v>700</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>701</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>700</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F85" s="15" t="s">
-        <v>702</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="11"/>
@@ -15148,7 +15230,7 @@
         <v>25</v>
       </c>
       <c r="L85" s="16" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
@@ -15163,19 +15245,19 @@
         <v>365</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G86" s="15"/>
       <c r="H86" s="11"/>
@@ -15189,7 +15271,7 @@
         <v>16</v>
       </c>
       <c r="L86" s="16" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="M86" s="12"/>
       <c r="N86" s="12"/>
@@ -15204,19 +15286,19 @@
         <v>368</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="11"/>
@@ -15230,7 +15312,7 @@
         <v>36</v>
       </c>
       <c r="L87" s="16" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="M87" s="12"/>
       <c r="N87" s="12"/>
@@ -15245,19 +15327,19 @@
         <v>371</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G88" s="15"/>
       <c r="H88" s="11"/>
@@ -15271,7 +15353,7 @@
         <v>60</v>
       </c>
       <c r="L88" s="16" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="M88" s="12"/>
       <c r="N88" s="12"/>
@@ -15286,19 +15368,19 @@
         <v>374</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="11"/>
@@ -15312,7 +15394,7 @@
         <v>24</v>
       </c>
       <c r="L89" s="16" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M89" s="12"/>
       <c r="N89" s="12"/>
@@ -15327,19 +15409,19 @@
         <v>377</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>108</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G90" s="15"/>
       <c r="H90" s="11"/>
@@ -15353,7 +15435,7 @@
         <v>0.5</v>
       </c>
       <c r="L90" s="16" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M90" s="12"/>
       <c r="N90" s="12"/>
@@ -15368,19 +15450,19 @@
         <v>381</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>108</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="11"/>
@@ -15394,7 +15476,7 @@
         <v>0.75</v>
       </c>
       <c r="L91" s="16" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="M91" s="12"/>
       <c r="N91" s="12"/>
@@ -15409,19 +15491,19 @@
         <v>384</v>
       </c>
       <c r="B92" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="D92" s="15" t="s">
         <v>716</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="E92" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F92" s="15" t="s">
         <v>717</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>718</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F92" s="15" t="s">
-        <v>719</v>
       </c>
       <c r="G92" s="15"/>
       <c r="H92" s="11"/>
@@ -15435,7 +15517,7 @@
         <v>12</v>
       </c>
       <c r="L92" s="16" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="M92" s="12"/>
       <c r="N92" s="12"/>
@@ -15450,19 +15532,19 @@
         <v>390</v>
       </c>
       <c r="B93" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="D93" s="15" t="s">
         <v>716</v>
       </c>
-      <c r="C93" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>718</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G93" s="15"/>
       <c r="H93" s="11"/>
@@ -15476,7 +15558,7 @@
         <v>12</v>
       </c>
       <c r="L93" s="16" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M93" s="12"/>
       <c r="N93" s="12"/>
@@ -15491,19 +15573,19 @@
         <v>393</v>
       </c>
       <c r="B94" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="D94" s="15" t="s">
         <v>716</v>
       </c>
-      <c r="C94" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>718</v>
-      </c>
       <c r="E94" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="11"/>
@@ -15517,7 +15599,7 @@
         <v>12</v>
       </c>
       <c r="L94" s="16" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="M94" s="12"/>
       <c r="N94" s="12"/>
@@ -15532,22 +15614,22 @@
         <v>396</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H95" s="11"/>
       <c r="I95" s="11">
@@ -15560,7 +15642,7 @@
         <v>6</v>
       </c>
       <c r="L95" s="16" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M95" s="12"/>
       <c r="N95" s="12"/>
@@ -15575,22 +15657,22 @@
         <v>396</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F96" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="G96" s="15" t="s">
         <v>726</v>
-      </c>
-      <c r="G96" s="15" t="s">
-        <v>728</v>
       </c>
       <c r="H96" s="11"/>
       <c r="I96" s="11">
@@ -15603,7 +15685,7 @@
         <v>8</v>
       </c>
       <c r="L96" s="16" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M96" s="12"/>
       <c r="N96" s="12"/>
@@ -15618,22 +15700,22 @@
         <v>396</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H97" s="11"/>
       <c r="I97" s="11">
@@ -15646,7 +15728,7 @@
         <v>10</v>
       </c>
       <c r="L97" s="16" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M97" s="12"/>
       <c r="N97" s="12"/>
@@ -15661,22 +15743,22 @@
         <v>401</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H98" s="11"/>
       <c r="I98" s="11">
@@ -15689,7 +15771,7 @@
         <v>6</v>
       </c>
       <c r="L98" s="16" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="M98" s="12"/>
       <c r="N98" s="12"/>
@@ -15704,22 +15786,22 @@
         <v>401</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H99" s="11"/>
       <c r="I99" s="11">
@@ -15732,7 +15814,7 @@
         <v>8</v>
       </c>
       <c r="L99" s="16" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="M99" s="12"/>
       <c r="N99" s="12"/>
@@ -15747,22 +15829,22 @@
         <v>401</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H100" s="11"/>
       <c r="I100" s="11">
@@ -15775,7 +15857,7 @@
         <v>10</v>
       </c>
       <c r="L100" s="16" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="M100" s="12"/>
       <c r="N100" s="12"/>
@@ -15790,22 +15872,22 @@
         <v>404</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H101" s="11"/>
       <c r="I101" s="11">
@@ -15818,7 +15900,7 @@
         <v>6</v>
       </c>
       <c r="L101" s="16" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
@@ -15833,22 +15915,22 @@
         <v>404</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H102" s="11"/>
       <c r="I102" s="11">
@@ -15861,7 +15943,7 @@
         <v>8</v>
       </c>
       <c r="L102" s="16" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M102" s="12"/>
       <c r="N102" s="12"/>
@@ -15876,22 +15958,22 @@
         <v>404</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H103" s="11"/>
       <c r="I103" s="11">
@@ -15904,7 +15986,7 @@
         <v>10</v>
       </c>
       <c r="L103" s="16" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
@@ -15919,22 +16001,22 @@
         <v>407</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H104" s="11"/>
       <c r="I104" s="11">
@@ -15947,7 +16029,7 @@
         <v>6</v>
       </c>
       <c r="L104" s="16" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="M104" s="12"/>
       <c r="N104" s="12"/>
@@ -15962,22 +16044,22 @@
         <v>407</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G105" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H105" s="11"/>
       <c r="I105" s="11">
@@ -15990,7 +16072,7 @@
         <v>8</v>
       </c>
       <c r="L105" s="16" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="M105" s="12"/>
       <c r="N105" s="12"/>
@@ -16005,22 +16087,22 @@
         <v>407</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H106" s="11"/>
       <c r="I106" s="11">
@@ -16033,7 +16115,7 @@
         <v>10</v>
       </c>
       <c r="L106" s="16" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="M106" s="12"/>
       <c r="N106" s="12"/>
@@ -16048,22 +16130,22 @@
         <v>410</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G107" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H107" s="11"/>
       <c r="I107" s="11">
@@ -16076,7 +16158,7 @@
         <v>6</v>
       </c>
       <c r="L107" s="16" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M107" s="12"/>
       <c r="N107" s="12"/>
@@ -16091,22 +16173,22 @@
         <v>410</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H108" s="11"/>
       <c r="I108" s="11">
@@ -16119,7 +16201,7 @@
         <v>8</v>
       </c>
       <c r="L108" s="16" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M108" s="12"/>
       <c r="N108" s="12"/>
@@ -16134,22 +16216,22 @@
         <v>410</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H109" s="11"/>
       <c r="I109" s="11">
@@ -16162,7 +16244,7 @@
         <v>10</v>
       </c>
       <c r="L109" s="16" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M109" s="12"/>
       <c r="N109" s="12"/>
@@ -16177,22 +16259,22 @@
         <v>413</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H110" s="11"/>
       <c r="I110" s="11">
@@ -16205,7 +16287,7 @@
         <v>6</v>
       </c>
       <c r="L110" s="16" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="M110" s="12"/>
       <c r="N110" s="12"/>
@@ -16220,22 +16302,22 @@
         <v>413</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H111" s="11"/>
       <c r="I111" s="11">
@@ -16248,7 +16330,7 @@
         <v>8</v>
       </c>
       <c r="L111" s="16" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="M111" s="12"/>
       <c r="N111" s="12"/>
@@ -16263,22 +16345,22 @@
         <v>413</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H112" s="11"/>
       <c r="I112" s="11">
@@ -16291,7 +16373,7 @@
         <v>10</v>
       </c>
       <c r="L112" s="16" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="M112" s="12"/>
       <c r="N112" s="12"/>
@@ -16306,22 +16388,22 @@
         <v>416</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H113" s="11"/>
       <c r="I113" s="11">
@@ -16334,7 +16416,7 @@
         <v>6</v>
       </c>
       <c r="L113" s="16" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="M113" s="12"/>
       <c r="N113" s="12"/>
@@ -16349,22 +16431,22 @@
         <v>416</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H114" s="11"/>
       <c r="I114" s="11">
@@ -16377,7 +16459,7 @@
         <v>8</v>
       </c>
       <c r="L114" s="16" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="M114" s="12"/>
       <c r="N114" s="12"/>
@@ -16392,22 +16474,22 @@
         <v>416</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F115" s="15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H115" s="11"/>
       <c r="I115" s="11">
@@ -16420,7 +16502,7 @@
         <v>10</v>
       </c>
       <c r="L115" s="16" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="M115" s="12"/>
       <c r="N115" s="12"/>
@@ -16435,22 +16517,22 @@
         <v>419</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H116" s="11"/>
       <c r="I116" s="11">
@@ -16463,7 +16545,7 @@
         <v>6</v>
       </c>
       <c r="L116" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="M116" s="12"/>
       <c r="N116" s="12"/>
@@ -16478,22 +16560,22 @@
         <v>419</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H117" s="11"/>
       <c r="I117" s="11">
@@ -16506,7 +16588,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="M117" s="12"/>
       <c r="N117" s="12"/>
@@ -16521,22 +16603,22 @@
         <v>419</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H118" s="11"/>
       <c r="I118" s="11">
@@ -16549,7 +16631,7 @@
         <v>10</v>
       </c>
       <c r="L118" s="16" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="M118" s="12"/>
       <c r="N118" s="12"/>
@@ -16564,22 +16646,22 @@
         <v>422</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H119" s="11"/>
       <c r="I119" s="11">
@@ -16592,7 +16674,7 @@
         <v>4</v>
       </c>
       <c r="L119" s="16" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M119" s="12"/>
       <c r="N119" s="12"/>
@@ -16607,22 +16689,22 @@
         <v>422</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H120" s="11"/>
       <c r="I120" s="11">
@@ -16635,7 +16717,7 @@
         <v>6</v>
       </c>
       <c r="L120" s="16" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M120" s="12"/>
       <c r="N120" s="12"/>
@@ -16650,22 +16732,22 @@
         <v>422</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G121" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H121" s="11"/>
       <c r="I121" s="11">
@@ -16678,7 +16760,7 @@
         <v>8</v>
       </c>
       <c r="L121" s="16" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M121" s="12"/>
       <c r="N121" s="12"/>
@@ -16693,22 +16775,22 @@
         <v>425</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H122" s="11"/>
       <c r="I122" s="11">
@@ -16721,7 +16803,7 @@
         <v>6</v>
       </c>
       <c r="L122" s="16" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="M122" s="12"/>
       <c r="N122" s="12"/>
@@ -16736,22 +16818,22 @@
         <v>425</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G123" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H123" s="11"/>
       <c r="I123" s="11">
@@ -16764,7 +16846,7 @@
         <v>8</v>
       </c>
       <c r="L123" s="16" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="M123" s="12"/>
       <c r="N123" s="12"/>
@@ -16779,22 +16861,22 @@
         <v>425</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H124" s="11"/>
       <c r="I124" s="11">
@@ -16807,7 +16889,7 @@
         <v>10</v>
       </c>
       <c r="L124" s="16" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="M124" s="12"/>
       <c r="N124" s="12"/>
@@ -16822,22 +16904,22 @@
         <v>428</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G125" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H125" s="11"/>
       <c r="I125" s="11">
@@ -16850,7 +16932,7 @@
         <v>4</v>
       </c>
       <c r="L125" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="M125" s="12"/>
       <c r="N125" s="12"/>
@@ -16865,22 +16947,22 @@
         <v>428</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H126" s="11"/>
       <c r="I126" s="11">
@@ -16893,7 +16975,7 @@
         <v>6</v>
       </c>
       <c r="L126" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="M126" s="12"/>
       <c r="N126" s="12"/>
@@ -16908,22 +16990,22 @@
         <v>428</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G127" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H127" s="11"/>
       <c r="I127" s="11">
@@ -16936,7 +17018,7 @@
         <v>8</v>
       </c>
       <c r="L127" s="16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="M127" s="12"/>
       <c r="N127" s="12"/>
@@ -16951,22 +17033,22 @@
         <v>431</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H128" s="11"/>
       <c r="I128" s="11">
@@ -16979,7 +17061,7 @@
         <v>6</v>
       </c>
       <c r="L128" s="16" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="M128" s="12"/>
       <c r="N128" s="12"/>
@@ -16994,22 +17076,22 @@
         <v>431</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F129" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G129" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H129" s="11"/>
       <c r="I129" s="11">
@@ -17022,7 +17104,7 @@
         <v>8</v>
       </c>
       <c r="L129" s="16" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="M129" s="12"/>
       <c r="N129" s="12"/>
@@ -17037,22 +17119,22 @@
         <v>431</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H130" s="11"/>
       <c r="I130" s="11">
@@ -17065,7 +17147,7 @@
         <v>10</v>
       </c>
       <c r="L130" s="16" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="M130" s="12"/>
       <c r="N130" s="12"/>
@@ -17080,22 +17162,22 @@
         <v>434</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G131" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H131" s="11"/>
       <c r="I131" s="11">
@@ -17108,7 +17190,7 @@
         <v>6</v>
       </c>
       <c r="L131" s="16" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="M131" s="12"/>
       <c r="N131" s="12"/>
@@ -17123,22 +17205,22 @@
         <v>434</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H132" s="11"/>
       <c r="I132" s="11">
@@ -17151,7 +17233,7 @@
         <v>8</v>
       </c>
       <c r="L132" s="16" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="M132" s="12"/>
       <c r="N132" s="12"/>
@@ -17166,22 +17248,22 @@
         <v>434</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F133" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G133" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H133" s="11"/>
       <c r="I133" s="11">
@@ -17194,7 +17276,7 @@
         <v>10</v>
       </c>
       <c r="L133" s="16" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="M133" s="12"/>
       <c r="N133" s="12"/>
@@ -17209,22 +17291,22 @@
         <v>437</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H134" s="11"/>
       <c r="I134" s="11">
@@ -17237,7 +17319,7 @@
         <v>6</v>
       </c>
       <c r="L134" s="16" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M134" s="12"/>
       <c r="N134" s="12"/>
@@ -17252,22 +17334,22 @@
         <v>437</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G135" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H135" s="11"/>
       <c r="I135" s="11">
@@ -17280,7 +17362,7 @@
         <v>8</v>
       </c>
       <c r="L135" s="16" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M135" s="12"/>
       <c r="N135" s="12"/>
@@ -17295,22 +17377,22 @@
         <v>437</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H136" s="11"/>
       <c r="I136" s="11">
@@ -17323,7 +17405,7 @@
         <v>10</v>
       </c>
       <c r="L136" s="16" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M136" s="12"/>
       <c r="N136" s="12"/>
@@ -17338,22 +17420,22 @@
         <v>441</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H137" s="11"/>
       <c r="I137" s="11">
@@ -17366,7 +17448,7 @@
         <v>6</v>
       </c>
       <c r="L137" s="16" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="M137" s="12"/>
       <c r="N137" s="12"/>
@@ -17381,22 +17463,22 @@
         <v>441</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H138" s="11"/>
       <c r="I138" s="11">
@@ -17409,7 +17491,7 @@
         <v>8</v>
       </c>
       <c r="L138" s="16" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="M138" s="12"/>
       <c r="N138" s="12"/>
@@ -17424,22 +17506,22 @@
         <v>441</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F139" s="15" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H139" s="11"/>
       <c r="I139" s="11">
@@ -17452,7 +17534,7 @@
         <v>10</v>
       </c>
       <c r="L139" s="16" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="M139" s="12"/>
       <c r="N139" s="12"/>
@@ -17467,22 +17549,22 @@
         <v>444</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H140" s="11"/>
       <c r="I140" s="11">
@@ -17495,7 +17577,7 @@
         <v>6</v>
       </c>
       <c r="L140" s="16" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M140" s="12"/>
       <c r="N140" s="12"/>
@@ -17510,22 +17592,22 @@
         <v>444</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F141" s="15" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G141" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H141" s="11"/>
       <c r="I141" s="11">
@@ -17538,7 +17620,7 @@
         <v>8</v>
       </c>
       <c r="L141" s="16" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M141" s="12"/>
       <c r="N141" s="12"/>
@@ -17553,22 +17635,22 @@
         <v>444</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H142" s="11"/>
       <c r="I142" s="11">
@@ -17581,7 +17663,7 @@
         <v>10</v>
       </c>
       <c r="L142" s="16" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M142" s="12"/>
       <c r="N142" s="12"/>
@@ -17596,22 +17678,22 @@
         <v>447</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F143" s="15" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G143" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H143" s="11"/>
       <c r="I143" s="11">
@@ -17624,7 +17706,7 @@
         <v>4</v>
       </c>
       <c r="L143" s="16" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M143" s="12"/>
       <c r="N143" s="12"/>
@@ -17639,22 +17721,22 @@
         <v>447</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H144" s="11"/>
       <c r="I144" s="11">
@@ -17667,7 +17749,7 @@
         <v>6</v>
       </c>
       <c r="L144" s="16" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M144" s="12"/>
       <c r="N144" s="12"/>
@@ -17682,22 +17764,22 @@
         <v>447</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H145" s="11"/>
       <c r="I145" s="11">
@@ -17710,7 +17792,7 @@
         <v>8</v>
       </c>
       <c r="L145" s="16" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M145" s="12"/>
       <c r="N145" s="12"/>
@@ -17725,22 +17807,22 @@
         <v>451</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H146" s="11"/>
       <c r="I146" s="11">
@@ -17753,7 +17835,7 @@
         <v>6</v>
       </c>
       <c r="L146" s="16" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="M146" s="12"/>
       <c r="N146" s="12"/>
@@ -17768,22 +17850,22 @@
         <v>451</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H147" s="11"/>
       <c r="I147" s="11">
@@ -17796,7 +17878,7 @@
         <v>8</v>
       </c>
       <c r="L147" s="16" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="M147" s="12"/>
       <c r="N147" s="12"/>
@@ -17811,22 +17893,22 @@
         <v>451</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H148" s="11"/>
       <c r="I148" s="11">
@@ -17839,7 +17921,7 @@
         <v>10</v>
       </c>
       <c r="L148" s="16" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="M148" s="12"/>
       <c r="N148" s="12"/>
@@ -17854,22 +17936,22 @@
         <v>454</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H149" s="11"/>
       <c r="I149" s="11">
@@ -17882,7 +17964,7 @@
         <v>6</v>
       </c>
       <c r="L149" s="16" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M149" s="12"/>
       <c r="N149" s="12"/>
@@ -17897,22 +17979,22 @@
         <v>454</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H150" s="11"/>
       <c r="I150" s="11">
@@ -17925,7 +18007,7 @@
         <v>8</v>
       </c>
       <c r="L150" s="16" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M150" s="12"/>
       <c r="N150" s="12"/>
@@ -17940,22 +18022,22 @@
         <v>454</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H151" s="11"/>
       <c r="I151" s="11">
@@ -17968,7 +18050,7 @@
         <v>10</v>
       </c>
       <c r="L151" s="16" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M151" s="12"/>
       <c r="N151" s="12"/>
@@ -17983,22 +18065,22 @@
         <v>457</v>
       </c>
       <c r="B152" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D152" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="E152" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F152" s="15" t="s">
         <v>768</v>
       </c>
-      <c r="D152" s="15" t="s">
-        <v>769</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F152" s="15" t="s">
-        <v>770</v>
-      </c>
       <c r="G152" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H152" s="11"/>
       <c r="I152" s="11">
@@ -18011,7 +18093,7 @@
         <v>10</v>
       </c>
       <c r="L152" s="16" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="M152" s="12"/>
       <c r="N152" s="12"/>
@@ -18026,22 +18108,22 @@
         <v>457</v>
       </c>
       <c r="B153" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C153" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D153" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C153" s="15" t="s">
+      <c r="E153" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F153" s="15" t="s">
         <v>768</v>
       </c>
-      <c r="D153" s="15" t="s">
-        <v>769</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F153" s="15" t="s">
-        <v>770</v>
-      </c>
       <c r="G153" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H153" s="11"/>
       <c r="I153" s="11">
@@ -18054,7 +18136,7 @@
         <v>12</v>
       </c>
       <c r="L153" s="16" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="M153" s="12"/>
       <c r="N153" s="12"/>
@@ -18069,22 +18151,22 @@
         <v>463</v>
       </c>
       <c r="B154" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C154" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D154" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C154" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D154" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E154" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H154" s="11"/>
       <c r="I154" s="11">
@@ -18097,7 +18179,7 @@
         <v>10</v>
       </c>
       <c r="L154" s="16" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="M154" s="12"/>
       <c r="N154" s="12"/>
@@ -18112,22 +18194,22 @@
         <v>463</v>
       </c>
       <c r="B155" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C155" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D155" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C155" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E155" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F155" s="15" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G155" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H155" s="11"/>
       <c r="I155" s="11">
@@ -18140,7 +18222,7 @@
         <v>12</v>
       </c>
       <c r="L155" s="16" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="M155" s="12"/>
       <c r="N155" s="12"/>
@@ -18155,22 +18237,22 @@
         <v>466</v>
       </c>
       <c r="B156" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C156" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D156" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C156" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E156" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H156" s="11"/>
       <c r="I156" s="11">
@@ -18183,7 +18265,7 @@
         <v>10</v>
       </c>
       <c r="L156" s="16" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="M156" s="12"/>
       <c r="N156" s="12"/>
@@ -18198,22 +18280,22 @@
         <v>466</v>
       </c>
       <c r="B157" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C157" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D157" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C157" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E157" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F157" s="15" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H157" s="11"/>
       <c r="I157" s="11">
@@ -18226,7 +18308,7 @@
         <v>12</v>
       </c>
       <c r="L157" s="16" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="M157" s="12"/>
       <c r="N157" s="12"/>
@@ -18241,22 +18323,22 @@
         <v>469</v>
       </c>
       <c r="B158" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C158" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D158" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C158" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E158" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H158" s="11"/>
       <c r="I158" s="11">
@@ -18269,7 +18351,7 @@
         <v>10</v>
       </c>
       <c r="L158" s="16" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M158" s="12"/>
       <c r="N158" s="12"/>
@@ -18284,22 +18366,22 @@
         <v>469</v>
       </c>
       <c r="B159" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C159" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D159" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C159" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E159" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F159" s="15" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H159" s="11"/>
       <c r="I159" s="11">
@@ -18312,7 +18394,7 @@
         <v>12</v>
       </c>
       <c r="L159" s="16" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M159" s="12"/>
       <c r="N159" s="12"/>
@@ -18327,22 +18409,22 @@
         <v>472</v>
       </c>
       <c r="B160" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D160" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C160" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D160" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E160" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H160" s="11"/>
       <c r="I160" s="11">
@@ -18355,7 +18437,7 @@
         <v>10</v>
       </c>
       <c r="L160" s="16" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="M160" s="12"/>
       <c r="N160" s="12"/>
@@ -18370,22 +18452,22 @@
         <v>472</v>
       </c>
       <c r="B161" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C161" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D161" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C161" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E161" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F161" s="15" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H161" s="11"/>
       <c r="I161" s="11">
@@ -18398,7 +18480,7 @@
         <v>12</v>
       </c>
       <c r="L161" s="16" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="M161" s="12"/>
       <c r="N161" s="12"/>
@@ -18413,22 +18495,22 @@
         <v>475</v>
       </c>
       <c r="B162" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D162" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C162" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D162" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E162" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H162" s="11"/>
       <c r="I162" s="11">
@@ -18441,7 +18523,7 @@
         <v>10</v>
       </c>
       <c r="L162" s="16" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="M162" s="12"/>
       <c r="N162" s="12"/>
@@ -18456,22 +18538,22 @@
         <v>475</v>
       </c>
       <c r="B163" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C163" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D163" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C163" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D163" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E163" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F163" s="15" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H163" s="11"/>
       <c r="I163" s="11">
@@ -18484,7 +18566,7 @@
         <v>12</v>
       </c>
       <c r="L163" s="16" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="M163" s="12"/>
       <c r="N163" s="12"/>
@@ -18499,22 +18581,22 @@
         <v>478</v>
       </c>
       <c r="B164" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C164" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D164" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C164" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D164" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E164" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H164" s="11"/>
       <c r="I164" s="11">
@@ -18527,7 +18609,7 @@
         <v>10</v>
       </c>
       <c r="L164" s="16" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M164" s="12"/>
       <c r="N164" s="12"/>
@@ -18542,22 +18624,22 @@
         <v>478</v>
       </c>
       <c r="B165" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C165" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D165" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C165" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D165" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E165" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F165" s="15" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="G165" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H165" s="11"/>
       <c r="I165" s="11">
@@ -18570,7 +18652,7 @@
         <v>12</v>
       </c>
       <c r="L165" s="16" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M165" s="12"/>
       <c r="N165" s="12"/>
@@ -18585,22 +18667,22 @@
         <v>481</v>
       </c>
       <c r="B166" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C166" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D166" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C166" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E166" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H166" s="11"/>
       <c r="I166" s="11">
@@ -18613,7 +18695,7 @@
         <v>10</v>
       </c>
       <c r="L166" s="16" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="M166" s="12"/>
       <c r="N166" s="12"/>
@@ -18628,22 +18710,22 @@
         <v>481</v>
       </c>
       <c r="B167" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D167" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C167" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D167" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E167" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F167" s="15" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H167" s="11"/>
       <c r="I167" s="11">
@@ -18656,7 +18738,7 @@
         <v>12</v>
       </c>
       <c r="L167" s="16" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="M167" s="12"/>
       <c r="N167" s="12"/>
@@ -18671,22 +18753,22 @@
         <v>484</v>
       </c>
       <c r="B168" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D168" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C168" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E168" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H168" s="11"/>
       <c r="I168" s="11">
@@ -18699,7 +18781,7 @@
         <v>10</v>
       </c>
       <c r="L168" s="16" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="M168" s="12"/>
       <c r="N168" s="12"/>
@@ -18714,22 +18796,22 @@
         <v>484</v>
       </c>
       <c r="B169" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C169" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D169" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C169" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E169" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F169" s="15" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G169" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H169" s="11"/>
       <c r="I169" s="11">
@@ -18742,7 +18824,7 @@
         <v>12</v>
       </c>
       <c r="L169" s="16" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="M169" s="12"/>
       <c r="N169" s="12"/>
@@ -18757,22 +18839,22 @@
         <v>487</v>
       </c>
       <c r="B170" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C170" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D170" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C170" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E170" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H170" s="11"/>
       <c r="I170" s="11">
@@ -18785,7 +18867,7 @@
         <v>10</v>
       </c>
       <c r="L170" s="16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="M170" s="12"/>
       <c r="N170" s="12"/>
@@ -18800,22 +18882,22 @@
         <v>487</v>
       </c>
       <c r="B171" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C171" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D171" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C171" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D171" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E171" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F171" s="15" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G171" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H171" s="11"/>
       <c r="I171" s="11">
@@ -18828,7 +18910,7 @@
         <v>12</v>
       </c>
       <c r="L171" s="16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="M171" s="12"/>
       <c r="N171" s="12"/>
@@ -18843,22 +18925,22 @@
         <v>490</v>
       </c>
       <c r="B172" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C172" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D172" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C172" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D172" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E172" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H172" s="11"/>
       <c r="I172" s="11">
@@ -18871,7 +18953,7 @@
         <v>10</v>
       </c>
       <c r="L172" s="16" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="M172" s="12"/>
       <c r="N172" s="12"/>
@@ -18886,22 +18968,22 @@
         <v>490</v>
       </c>
       <c r="B173" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C173" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D173" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C173" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="D173" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E173" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F173" s="15" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G173" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H173" s="11"/>
       <c r="I173" s="11">
@@ -18914,7 +18996,7 @@
         <v>12</v>
       </c>
       <c r="L173" s="16" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="M173" s="12"/>
       <c r="N173" s="12"/>
@@ -18929,22 +19011,22 @@
         <v>493</v>
       </c>
       <c r="B174" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C174" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="D174" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C174" s="15" t="s">
-        <v>792</v>
-      </c>
-      <c r="D174" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E174" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H174" s="11"/>
       <c r="I174" s="11">
@@ -18957,7 +19039,7 @@
         <v>10</v>
       </c>
       <c r="L174" s="16" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="M174" s="12"/>
       <c r="N174" s="12"/>
@@ -18972,22 +19054,22 @@
         <v>493</v>
       </c>
       <c r="B175" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C175" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="D175" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C175" s="15" t="s">
-        <v>792</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E175" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F175" s="15" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H175" s="11"/>
       <c r="I175" s="11">
@@ -19000,7 +19082,7 @@
         <v>12</v>
       </c>
       <c r="L175" s="16" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -19012,25 +19094,25 @@
     </row>
     <row r="176" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B176" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C176" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="D176" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C176" s="15" t="s">
-        <v>792</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E176" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H176" s="11"/>
       <c r="I176" s="11">
@@ -19043,7 +19125,7 @@
         <v>5</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="M176" s="12"/>
       <c r="N176" s="12"/>
@@ -19055,25 +19137,25 @@
     </row>
     <row r="177" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B177" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C177" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="D177" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C177" s="15" t="s">
-        <v>792</v>
-      </c>
-      <c r="D177" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E177" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F177" s="15" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H177" s="11"/>
       <c r="I177" s="11">
@@ -19086,7 +19168,7 @@
         <v>10</v>
       </c>
       <c r="L177" s="16" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="M177" s="12"/>
       <c r="N177" s="12"/>
@@ -19098,22 +19180,22 @@
     </row>
     <row r="178" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B178" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C178" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="D178" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C178" s="15" t="s">
-        <v>792</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E178" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G178" s="15"/>
       <c r="H178" s="11"/>
@@ -19127,7 +19209,7 @@
         <v>12</v>
       </c>
       <c r="L178" s="16" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="M178" s="12"/>
       <c r="N178" s="12"/>
@@ -19139,25 +19221,25 @@
     </row>
     <row r="179" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B179" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C179" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="D179" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C179" s="15" t="s">
-        <v>799</v>
-      </c>
-      <c r="D179" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E179" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F179" s="15" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H179" s="11"/>
       <c r="I179" s="11">
@@ -19170,7 +19252,7 @@
         <v>25</v>
       </c>
       <c r="L179" s="16" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="M179" s="12"/>
       <c r="N179" s="12"/>
@@ -19182,25 +19264,25 @@
     </row>
     <row r="180" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B180" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C180" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="D180" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C180" s="15" t="s">
-        <v>799</v>
-      </c>
-      <c r="D180" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E180" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H180" s="11"/>
       <c r="I180" s="11">
@@ -19213,7 +19295,7 @@
         <v>30</v>
       </c>
       <c r="L180" s="16" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="M180" s="12"/>
       <c r="N180" s="12"/>
@@ -19225,22 +19307,22 @@
     </row>
     <row r="181" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B181" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="C181" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="D181" s="15" t="s">
         <v>767</v>
       </c>
-      <c r="C181" s="15" t="s">
-        <v>799</v>
-      </c>
-      <c r="D181" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="E181" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F181" s="15" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G181" s="15"/>
       <c r="H181" s="11"/>
@@ -19254,7 +19336,7 @@
         <v>10</v>
       </c>
       <c r="L181" s="16" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="M181" s="12"/>
       <c r="N181" s="12"/>
@@ -19266,22 +19348,22 @@
     </row>
     <row r="182" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G182" s="15"/>
       <c r="H182" s="11"/>
@@ -19295,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="16" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="M182" s="12"/>
       <c r="N182" s="12"/>
@@ -19307,22 +19389,22 @@
     </row>
     <row r="183" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C183" s="15" t="s">
+        <v>803</v>
+      </c>
+      <c r="D183" s="15" t="s">
+        <v>803</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F183" s="15" t="s">
         <v>805</v>
-      </c>
-      <c r="D183" s="15" t="s">
-        <v>805</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="F183" s="15" t="s">
-        <v>807</v>
       </c>
       <c r="G183" s="15"/>
       <c r="H183" s="11"/>
@@ -19336,7 +19418,7 @@
         <v>4</v>
       </c>
       <c r="L183" s="16" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="M183" s="12"/>
       <c r="N183" s="12"/>
@@ -20591,121 +20673,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>824</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>825</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>826</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>827</v>
-      </c>
       <c r="E1" s="17" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="27.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>827</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>828</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="D2" s="18" t="s">
         <v>829</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="E2" s="18" t="s">
         <v>830</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>831</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>832</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>833</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="D3" s="18" t="s">
         <v>834</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>835</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>836</v>
-      </c>
       <c r="E3" s="18" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>827</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>837</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>829</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>838</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>836</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>839</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>840</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="D5" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>841</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>842</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>836</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>843</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>844</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="D6" s="18" t="s">
+        <v>834</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>845</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>846</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>836</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="17" t="s">
+        <v>846</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>848</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>849</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>850</v>
-      </c>
       <c r="D7" s="18" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
   </sheetData>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\new app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D638AF89-EDE4-4E98-9A76-66498603A81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BD4E50-0626-4B4D-BF94-DD1516D5C7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="865">
   <si>
     <t>Contact</t>
   </si>
@@ -2596,32 +2596,52 @@
     <t>Max File Size recommended</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM001.jpg
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM007.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg</t>
+  </si>
+  <si>
+    <t>Karak Tea 1</t>
+  </si>
+  <si>
+    <t>Karak Tea 3</t>
+  </si>
+  <si>
+    <t>Karak Tea 4</t>
+  </si>
+  <si>
+    <t>Karak Tea 5</t>
+  </si>
+  <si>
+    <t>Karak Tea 6</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM001.jpg
 /ItemImages</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM007.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg</t>
-  </si>
-  <si>
-    <t>Karak Tea 1</t>
-  </si>
-  <si>
-    <t>Karak Tea 3</t>
-  </si>
-  <si>
-    <t>Karak Tea 4</t>
-  </si>
-  <si>
-    <t>Karak Tea 5</t>
-  </si>
-  <si>
-    <t>Karak Tea 6</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM007.jpg
+/ItemImages</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM008.jpg
+/ItemImages</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM001.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM003.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM008.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM009.jpg</t>
   </si>
 </sst>
 </file>
@@ -3577,7 +3597,7 @@
     <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.89453125" customWidth="1"/>
-    <col min="5" max="5" width="17.26171875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="64.3671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.3125" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.1015625" customWidth="1"/>
     <col min="8" max="8" width="11.47265625" style="1" customWidth="1"/>
@@ -3646,7 +3666,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18" ht="48.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
@@ -3660,7 +3680,7 @@
         <v>133</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>134</v>
@@ -3684,14 +3704,14 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18" ht="57.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11" t="s">
         <v>29</v>
       </c>
@@ -3705,7 +3725,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>136</v>
@@ -3731,7 +3751,7 @@
       </c>
       <c r="N3" s="12"/>
       <c r="O3" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="11" t="b">
@@ -3752,7 +3772,7 @@
         <v>133</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>138</v>
@@ -3778,7 +3798,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P4" s="12"/>
       <c r="Q4" s="11" t="b">
@@ -3799,7 +3819,7 @@
         <v>133</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>140</v>
@@ -3825,7 +3845,7 @@
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="b">
@@ -3846,7 +3866,7 @@
         <v>133</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>142</v>
@@ -3872,7 +3892,7 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="11" t="b">
@@ -3893,7 +3913,7 @@
         <v>133</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>144</v>
@@ -3919,7 +3939,7 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="11" t="b">
@@ -3940,7 +3960,7 @@
         <v>133</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>146</v>
@@ -3966,7 +3986,7 @@
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P8" s="12"/>
       <c r="Q8" s="11" t="b">
@@ -3990,7 +4010,7 @@
         <v>133</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>148</v>
@@ -4016,7 +4036,7 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P9" s="12"/>
       <c r="Q9" s="11" t="b">
@@ -4037,7 +4057,7 @@
         <v>133</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>151</v>
@@ -4063,7 +4083,7 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P10" s="12"/>
       <c r="Q10" s="11" t="b">
@@ -4084,7 +4104,7 @@
         <v>133</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>153</v>
@@ -4110,7 +4130,7 @@
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="11" t="b">
@@ -4131,7 +4151,7 @@
         <v>133</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>156</v>
@@ -4157,7 +4177,7 @@
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P12" s="12"/>
       <c r="Q12" s="11" t="b">
@@ -4178,7 +4198,7 @@
         <v>133</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>158</v>
@@ -4204,7 +4224,7 @@
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="11" t="b">
@@ -4225,7 +4245,7 @@
         <v>133</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>161</v>
@@ -4251,7 +4271,7 @@
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P14" s="12"/>
       <c r="Q14" s="11" t="b">
@@ -4271,8 +4291,8 @@
       <c r="D15" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>851</v>
+      <c r="E15" s="8" t="s">
+        <v>862</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>166</v>
@@ -4298,7 +4318,7 @@
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="P15" s="12"/>
       <c r="Q15" s="11" t="b">
@@ -4321,8 +4341,8 @@
       <c r="D16" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>851</v>
+      <c r="E16" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>169</v>
@@ -4362,8 +4382,8 @@
       <c r="D17" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>851</v>
+      <c r="E17" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>172</v>
@@ -4403,8 +4423,8 @@
       <c r="D18" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>851</v>
+      <c r="E18" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>175</v>
@@ -4444,8 +4464,8 @@
       <c r="D19" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>851</v>
+      <c r="E19" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>178</v>
@@ -4487,8 +4507,8 @@
       <c r="D20" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>851</v>
+      <c r="E20" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>181</v>
@@ -4528,8 +4548,8 @@
       <c r="D21" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>851</v>
+      <c r="E21" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>184</v>
@@ -4569,8 +4589,8 @@
       <c r="D22" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>851</v>
+      <c r="E22" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>188</v>
@@ -4610,8 +4630,8 @@
       <c r="D23" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>851</v>
+      <c r="E23" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>191</v>
@@ -4656,8 +4676,8 @@
       <c r="D24" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>851</v>
+      <c r="E24" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>194</v>
@@ -4697,8 +4717,8 @@
       <c r="D25" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>851</v>
+      <c r="E25" s="8" t="s">
+        <v>859</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>197</v>
@@ -4743,7 +4763,7 @@
         <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>199</v>
@@ -4788,7 +4808,7 @@
         <v>165</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>202</v>
@@ -4829,7 +4849,7 @@
         <v>165</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>205</v>
@@ -4870,7 +4890,7 @@
         <v>165</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>208</v>
@@ -4911,7 +4931,7 @@
         <v>165</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>213</v>
@@ -4952,7 +4972,7 @@
         <v>165</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>216</v>
@@ -4993,7 +5013,7 @@
         <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>219</v>
@@ -5034,7 +5054,7 @@
         <v>165</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>222</v>
@@ -5075,7 +5095,7 @@
         <v>165</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>225</v>
@@ -5116,7 +5136,7 @@
         <v>165</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>228</v>
@@ -5157,7 +5177,7 @@
         <v>165</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>231</v>
@@ -5198,7 +5218,7 @@
         <v>165</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>235</v>
@@ -5239,7 +5259,7 @@
         <v>165</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>238</v>
@@ -5282,7 +5302,7 @@
         <v>165</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>241</v>
@@ -5323,7 +5343,7 @@
         <v>165</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>246</v>
@@ -5364,7 +5384,7 @@
         <v>165</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>249</v>
@@ -5405,7 +5425,7 @@
         <v>165</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>252</v>
@@ -5448,7 +5468,7 @@
         <v>165</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>255</v>
@@ -5491,7 +5511,7 @@
         <v>165</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>197</v>
@@ -5534,7 +5554,7 @@
         <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>261</v>
@@ -5577,7 +5597,7 @@
         <v>165</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>264</v>
@@ -5618,7 +5638,7 @@
         <v>165</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>268</v>
@@ -5658,8 +5678,8 @@
       <c r="D48" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>852</v>
+      <c r="E48" s="8" t="s">
+        <v>863</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>274</v>
@@ -5700,7 +5720,7 @@
         <v>273</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>277</v>
@@ -5741,7 +5761,7 @@
         <v>273</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>281</v>
@@ -5785,7 +5805,7 @@
         <v>273</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>277</v>
@@ -5828,7 +5848,7 @@
         <v>273</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>286</v>
@@ -5869,7 +5889,7 @@
         <v>273</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>289</v>
@@ -5910,7 +5930,7 @@
         <v>273</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>292</v>
@@ -5951,7 +5971,7 @@
         <v>273</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>295</v>
@@ -5992,7 +6012,7 @@
         <v>273</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>298</v>
@@ -6033,7 +6053,7 @@
         <v>273</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>302</v>
@@ -6074,7 +6094,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>305</v>
@@ -6115,7 +6135,7 @@
         <v>273</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>308</v>
@@ -6156,7 +6176,7 @@
         <v>273</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>311</v>
@@ -6199,7 +6219,7 @@
         <v>273</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>314</v>
@@ -6240,7 +6260,7 @@
         <v>273</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>317</v>
@@ -6281,7 +6301,7 @@
         <v>273</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>321</v>
@@ -6322,7 +6342,7 @@
         <v>273</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>324</v>
@@ -6363,7 +6383,7 @@
         <v>273</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>327</v>
@@ -6403,8 +6423,8 @@
       <c r="D66" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>852</v>
+      <c r="E66" s="8" t="s">
+        <v>864</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>332</v>
@@ -6448,8 +6468,8 @@
       <c r="D67" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>852</v>
+      <c r="E67" s="8" t="s">
+        <v>860</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>334</v>
@@ -6493,8 +6513,8 @@
       <c r="D68" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>852</v>
+      <c r="E68" s="8" t="s">
+        <v>860</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>336</v>
@@ -6541,8 +6561,8 @@
       <c r="D69" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>852</v>
+      <c r="E69" s="8" t="s">
+        <v>860</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>338</v>
@@ -6589,7 +6609,7 @@
         <v>331</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>338</v>
@@ -6636,7 +6656,7 @@
         <v>331</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>342</v>
@@ -6681,7 +6701,7 @@
         <v>331</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>345</v>
@@ -6728,7 +6748,7 @@
         <v>331</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>345</v>
@@ -6777,7 +6797,7 @@
         <v>331</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>347</v>
@@ -6826,7 +6846,7 @@
         <v>331</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>347</v>
@@ -6875,7 +6895,7 @@
         <v>331</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F76" s="12" t="s">
         <v>349</v>
@@ -6922,7 +6942,7 @@
         <v>331</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>349</v>
@@ -6969,7 +6989,7 @@
         <v>331</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>351</v>
@@ -7016,7 +7036,7 @@
         <v>331</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>351</v>
@@ -7063,7 +7083,7 @@
         <v>331</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F80" s="12" t="s">
         <v>353</v>
@@ -7110,7 +7130,7 @@
         <v>331</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>353</v>
@@ -7157,7 +7177,7 @@
         <v>331</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>355</v>
@@ -7204,7 +7224,7 @@
         <v>331</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>355</v>
@@ -7251,7 +7271,7 @@
         <v>331</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>358</v>
@@ -9990,7 +10010,7 @@
         <v>387</v>
       </c>
       <c r="C148" s="19" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D148" s="12" t="s">
         <v>387</v>
@@ -10033,7 +10053,7 @@
         <v>387</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D149" s="12" t="s">
         <v>387</v>
@@ -10076,7 +10096,7 @@
         <v>387</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D150" s="12" t="s">
         <v>387</v>
@@ -10119,7 +10139,7 @@
         <v>387</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D151" s="12" t="s">
         <v>387</v>
@@ -10337,7 +10357,7 @@
         <v>458</v>
       </c>
       <c r="C156" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D156" s="12" t="s">
         <v>460</v>
@@ -10380,7 +10400,7 @@
         <v>458</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D157" s="12" t="s">
         <v>460</v>
@@ -10423,7 +10443,7 @@
         <v>458</v>
       </c>
       <c r="C158" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D158" s="12" t="s">
         <v>460</v>
@@ -10466,7 +10486,7 @@
         <v>458</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D159" s="12" t="s">
         <v>460</v>
@@ -10509,7 +10529,7 @@
         <v>458</v>
       </c>
       <c r="C160" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D160" s="12" t="s">
         <v>460</v>
@@ -10552,7 +10572,7 @@
         <v>458</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D161" s="12" t="s">
         <v>460</v>
@@ -10595,7 +10615,7 @@
         <v>458</v>
       </c>
       <c r="C162" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D162" s="12" t="s">
         <v>460</v>
@@ -10638,7 +10658,7 @@
         <v>458</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D163" s="12" t="s">
         <v>460</v>
@@ -10681,7 +10701,7 @@
         <v>458</v>
       </c>
       <c r="C164" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D164" s="12" t="s">
         <v>460</v>
@@ -10724,7 +10744,7 @@
         <v>458</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>460</v>
@@ -10767,7 +10787,7 @@
         <v>458</v>
       </c>
       <c r="C166" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>460</v>
@@ -10810,7 +10830,7 @@
         <v>458</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D167" s="12" t="s">
         <v>460</v>
@@ -10853,7 +10873,7 @@
         <v>458</v>
       </c>
       <c r="C168" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D168" s="12" t="s">
         <v>460</v>
@@ -10896,7 +10916,7 @@
         <v>458</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D169" s="12" t="s">
         <v>460</v>
@@ -10939,7 +10959,7 @@
         <v>458</v>
       </c>
       <c r="C170" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D170" s="12" t="s">
         <v>460</v>
@@ -10982,7 +11002,7 @@
         <v>458</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D171" s="12" t="s">
         <v>460</v>
@@ -11025,7 +11045,7 @@
         <v>458</v>
       </c>
       <c r="C172" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D172" s="12" t="s">
         <v>460</v>
@@ -11068,7 +11088,7 @@
         <v>458</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D173" s="12" t="s">
         <v>460</v>
@@ -11111,7 +11131,7 @@
         <v>458</v>
       </c>
       <c r="C174" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D174" s="12" t="s">
         <v>460</v>
@@ -11154,7 +11174,7 @@
         <v>458</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D175" s="12" t="s">
         <v>460</v>
@@ -11197,7 +11217,7 @@
         <v>458</v>
       </c>
       <c r="C176" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D176" s="12" t="s">
         <v>460</v>
@@ -11240,7 +11260,7 @@
         <v>458</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D177" s="12" t="s">
         <v>460</v>
@@ -11283,7 +11303,7 @@
         <v>458</v>
       </c>
       <c r="C178" s="19" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D178" s="12" t="s">
         <v>460</v>
@@ -11324,7 +11344,7 @@
         <v>458</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>460</v>
@@ -11367,7 +11387,7 @@
         <v>458</v>
       </c>
       <c r="C180" s="19" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>460</v>
@@ -11410,7 +11430,7 @@
         <v>458</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D181" s="12" t="s">
         <v>460</v>
@@ -11536,15 +11556,15 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{8DE9E557-F3B0-434E-98AC-B26B26771AD6}"/>
-    <hyperlink ref="E3:E14" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM001.jpg_x000a_/ItemImages" xr:uid="{DD02AF20-9319-4EFF-888A-177906FC7290}"/>
-    <hyperlink ref="E15" r:id="rId3" xr:uid="{4D05D8FA-37AC-4FE4-A4B6-56782248FA97}"/>
-    <hyperlink ref="E16:E47" r:id="rId4" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM007.jpg" xr:uid="{39724CD9-AE3A-4BCE-99F4-A1A3845A2CB7}"/>
-    <hyperlink ref="E48" r:id="rId5" xr:uid="{3F243788-E863-45B9-815B-BAFC290A401E}"/>
-    <hyperlink ref="E49:E65" r:id="rId6" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg" xr:uid="{84C1ACAE-469E-4E4B-A0FF-2358629AD8EB}"/>
-    <hyperlink ref="E66" r:id="rId7" xr:uid="{E2559F05-4803-4BA3-B273-A550232E8854}"/>
-    <hyperlink ref="E67:E84" r:id="rId8" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg" xr:uid="{1342928F-E905-4149-B20A-08B975EABE45}"/>
-    <hyperlink ref="O2" r:id="rId9" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{D2746854-1D7F-4CD4-91B9-FA32C9E32A74}"/>
-    <hyperlink ref="O3:O15" r:id="rId10" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{C8CECB9D-E2EF-49B9-ADDC-D699A1C77B63}"/>
+    <hyperlink ref="E49:E65" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg" xr:uid="{84C1ACAE-469E-4E4B-A0FF-2358629AD8EB}"/>
+    <hyperlink ref="O2" r:id="rId3" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{D2746854-1D7F-4CD4-91B9-FA32C9E32A74}"/>
+    <hyperlink ref="O3:O15" r:id="rId4" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{C8CECB9D-E2EF-49B9-ADDC-D699A1C77B63}"/>
+    <hyperlink ref="E3:E14" r:id="rId5" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM001.jpg_x000a_/ItemImages" xr:uid="{4ABF00A0-51EA-4D32-A351-19B3A8E5EC6E}"/>
+    <hyperlink ref="E16:E25" r:id="rId6" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM007.jpg_x000a_/ItemImages" xr:uid="{3BCA7EB0-7841-4375-9CE4-7EF582A60F3C}"/>
+    <hyperlink ref="E48" r:id="rId7" xr:uid="{2F41CBBF-D68F-4D63-B77F-057038496B72}"/>
+    <hyperlink ref="E66" r:id="rId8" xr:uid="{EF3BC6C2-E1F6-4A27-9C17-FE0C5EB513D8}"/>
+    <hyperlink ref="E67:E69" r:id="rId9" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM008.jpg_x000a_/ItemImages" xr:uid="{49EE5850-C7AD-4F92-AE3D-EF66876F02D0}"/>
+    <hyperlink ref="E15" r:id="rId10" xr:uid="{5E13716E-CA48-4303-A0EE-4996DD259711}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\new app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BD4E50-0626-4B4D-BF94-DD1516D5C7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E4A679-70BA-4964-A2AC-70AA575EE723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="866">
   <si>
     <t>Contact</t>
   </si>
@@ -2632,16 +2632,19 @@
 /ItemImages</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM001.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM003.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM008.jpg</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM009.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/ItemImages/ITM001.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/ItemImages/ITM002.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/ItemImages/ITM007.jpg</t>
   </si>
 </sst>
 </file>
@@ -3475,7 +3478,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" tooltip="Banner02.jpg" display="https://github.com/Rmoosa2014/Restaurant-menu/blob/main/images/banner/Banner02.jpg" xr:uid="{1AA01F29-999B-4367-883C-4232785B746E}"/>
-    <hyperlink ref="N2" r:id="rId2" display="https://raw.githubusercontent.com/DigiDatas/KARAK-WA-KARAK/main/logo.png" xr:uid="{A1FB07C3-B8F2-49A0-A23A-B1A95E6708A3}"/>
+    <hyperlink ref="N2" r:id="rId2" xr:uid="{A1FB07C3-B8F2-49A0-A23A-B1A95E6708A3}"/>
     <hyperlink ref="O2" r:id="rId3" display="https://raw.githubusercontent.com/DigiDatas/ShawarMax-Al-Manar/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/DigiDatas/ShawarMax-Al-Manar/main/images/banner/Banner02.jpg" xr:uid="{81AFF1C3-240D-468E-995A-5B6703C1D34C}"/>
     <hyperlink ref="I2" r:id="rId4" location="Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" display="https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end" xr:uid="{D3138493-AF89-421B-991A-F6B48A9858C5}"/>
   </hyperlinks>
@@ -3680,7 +3683,7 @@
         <v>133</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>134</v>
@@ -4292,7 +4295,7 @@
         <v>165</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>166</v>
@@ -4763,7 +4766,7 @@
         <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>199</v>
@@ -5679,7 +5682,7 @@
         <v>273</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>274</v>
@@ -6424,7 +6427,7 @@
         <v>331</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>332</v>
@@ -11564,7 +11567,8 @@
     <hyperlink ref="E48" r:id="rId7" xr:uid="{2F41CBBF-D68F-4D63-B77F-057038496B72}"/>
     <hyperlink ref="E66" r:id="rId8" xr:uid="{EF3BC6C2-E1F6-4A27-9C17-FE0C5EB513D8}"/>
     <hyperlink ref="E67:E69" r:id="rId9" display="https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ItemImages/ITM008.jpg_x000a_/ItemImages" xr:uid="{49EE5850-C7AD-4F92-AE3D-EF66876F02D0}"/>
-    <hyperlink ref="E15" r:id="rId10" xr:uid="{5E13716E-CA48-4303-A0EE-4996DD259711}"/>
+    <hyperlink ref="E15" r:id="rId10" xr:uid="{FAB46719-85EC-4B5D-B821-3171F47483EB}"/>
+    <hyperlink ref="E26" r:id="rId11" xr:uid="{6096A54B-653A-4F3F-82E1-8C4033A5716D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\Firoz\Usthat Hotel\new app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E4A679-70BA-4964-A2AC-70AA575EE723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF2CDE0-D6F7-4751-8876-A24CC90748AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="RelatedItems" sheetId="6" r:id="rId5"/>
     <sheet name="Image sizes" sheetId="7" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Menu-English'!$A$1:$R$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2602,21 +2605,6 @@
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/images/ITM005.jpg</t>
   </si>
   <si>
-    <t>Karak Tea 1</t>
-  </si>
-  <si>
-    <t>Karak Tea 3</t>
-  </si>
-  <si>
-    <t>Karak Tea 4</t>
-  </si>
-  <si>
-    <t>Karak Tea 5</t>
-  </si>
-  <si>
-    <t>Karak Tea 6</t>
-  </si>
-  <si>
     <t>https://www.instagram.com,https://maps.app.goo.gl/qBs9KMJqMjmNzuBG6#Intent;scheme=http;package=com.google.android.apps.maps;S.browser_fallback_url=https://www.google.com/maps/place//data%3D!4m2!3m1!1s0x3e2f09004674413b:0x42773bc4f4454fad!11m1!4b1%3Fentry%3Ds&amp;sa%3DX&amp;ved%3D2ahUKEwjprvv61o6XAxVB9wIHHeRUC_4Q4kB6BAgEEAA;end</t>
   </si>
   <si>
@@ -2645,6 +2633,21 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/DigiDatas/usthad-azeezia-menu/main/images/ItemImages/ITM007.jpg</t>
+  </si>
+  <si>
+    <t>Karak Tea-01</t>
+  </si>
+  <si>
+    <t>Karak Tea-02</t>
+  </si>
+  <si>
+    <t>Karak Tea-03</t>
+  </si>
+  <si>
+    <t>Karak Tea-04</t>
+  </si>
+  <si>
+    <t>Karak Tea-05</t>
   </si>
 </sst>
 </file>
@@ -3683,7 +3686,7 @@
         <v>133</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>134</v>
@@ -3707,7 +3710,7 @@
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="11" t="b">
@@ -3728,7 +3731,7 @@
         <v>133</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>136</v>
@@ -3754,7 +3757,7 @@
       </c>
       <c r="N3" s="12"/>
       <c r="O3" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="11" t="b">
@@ -3775,7 +3778,7 @@
         <v>133</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>138</v>
@@ -3801,7 +3804,7 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P4" s="12"/>
       <c r="Q4" s="11" t="b">
@@ -3822,7 +3825,7 @@
         <v>133</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>140</v>
@@ -3848,7 +3851,7 @@
       </c>
       <c r="N5" s="12"/>
       <c r="O5" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="b">
@@ -3869,7 +3872,7 @@
         <v>133</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>142</v>
@@ -3895,7 +3898,7 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P6" s="12"/>
       <c r="Q6" s="11" t="b">
@@ -3916,7 +3919,7 @@
         <v>133</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>144</v>
@@ -3942,7 +3945,7 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P7" s="12"/>
       <c r="Q7" s="11" t="b">
@@ -3963,7 +3966,7 @@
         <v>133</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>146</v>
@@ -3989,7 +3992,7 @@
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P8" s="12"/>
       <c r="Q8" s="11" t="b">
@@ -4013,7 +4016,7 @@
         <v>133</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>148</v>
@@ -4039,7 +4042,7 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P9" s="12"/>
       <c r="Q9" s="11" t="b">
@@ -4060,7 +4063,7 @@
         <v>133</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>151</v>
@@ -4086,7 +4089,7 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P10" s="12"/>
       <c r="Q10" s="11" t="b">
@@ -4107,7 +4110,7 @@
         <v>133</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>153</v>
@@ -4133,7 +4136,7 @@
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="11" t="b">
@@ -4154,7 +4157,7 @@
         <v>133</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>156</v>
@@ -4180,7 +4183,7 @@
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P12" s="12"/>
       <c r="Q12" s="11" t="b">
@@ -4201,7 +4204,7 @@
         <v>133</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>158</v>
@@ -4227,7 +4230,7 @@
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="11" t="b">
@@ -4248,7 +4251,7 @@
         <v>133</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>161</v>
@@ -4274,7 +4277,7 @@
       </c>
       <c r="N14" s="12"/>
       <c r="O14" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P14" s="12"/>
       <c r="Q14" s="11" t="b">
@@ -4295,7 +4298,7 @@
         <v>165</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>166</v>
@@ -4321,7 +4324,7 @@
       </c>
       <c r="N15" s="12"/>
       <c r="O15" s="20" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="P15" s="12"/>
       <c r="Q15" s="11" t="b">
@@ -4345,7 +4348,7 @@
         <v>165</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>169</v>
@@ -4386,7 +4389,7 @@
         <v>165</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>172</v>
@@ -4427,7 +4430,7 @@
         <v>165</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>175</v>
@@ -4468,7 +4471,7 @@
         <v>165</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>178</v>
@@ -4511,7 +4514,7 @@
         <v>165</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>181</v>
@@ -4552,7 +4555,7 @@
         <v>165</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>184</v>
@@ -4593,7 +4596,7 @@
         <v>165</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>188</v>
@@ -4634,7 +4637,7 @@
         <v>165</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>191</v>
@@ -4680,7 +4683,7 @@
         <v>165</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>194</v>
@@ -4721,7 +4724,7 @@
         <v>165</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>197</v>
@@ -4766,7 +4769,7 @@
         <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>199</v>
@@ -5682,7 +5685,7 @@
         <v>273</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>274</v>
@@ -6427,7 +6430,7 @@
         <v>331</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>332</v>
@@ -6472,7 +6475,7 @@
         <v>331</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>334</v>
@@ -6517,7 +6520,7 @@
         <v>331</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>336</v>
@@ -6565,7 +6568,7 @@
         <v>331</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>338</v>
@@ -6845,8 +6848,8 @@
       <c r="C75" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>331</v>
+      <c r="D75" s="19" t="s">
+        <v>862</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>851</v>
@@ -6894,8 +6897,8 @@
       <c r="C76" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D76" s="12" t="s">
-        <v>331</v>
+      <c r="D76" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>851</v>
@@ -6941,8 +6944,8 @@
       <c r="C77" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>331</v>
+      <c r="D77" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>851</v>
@@ -6988,8 +6991,8 @@
       <c r="C78" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>331</v>
+      <c r="D78" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>851</v>
@@ -7035,8 +7038,8 @@
       <c r="C79" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D79" s="12" t="s">
-        <v>331</v>
+      <c r="D79" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>851</v>
@@ -7082,8 +7085,8 @@
       <c r="C80" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D80" s="12" t="s">
-        <v>331</v>
+      <c r="D80" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>851</v>
@@ -7129,8 +7132,8 @@
       <c r="C81" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D81" s="12" t="s">
-        <v>331</v>
+      <c r="D81" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>851</v>
@@ -7176,8 +7179,8 @@
       <c r="C82" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="D82" s="12" t="s">
-        <v>331</v>
+      <c r="D82" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>851</v>
@@ -9327,8 +9330,8 @@
       <c r="C132" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="D132" s="12" t="s">
-        <v>387</v>
+      <c r="D132" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>819</v>
@@ -9370,8 +9373,8 @@
       <c r="C133" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="D133" s="12" t="s">
-        <v>387</v>
+      <c r="D133" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>819</v>
@@ -9413,8 +9416,8 @@
       <c r="C134" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D134" s="12" t="s">
-        <v>387</v>
+      <c r="D134" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>819</v>
@@ -9456,8 +9459,8 @@
       <c r="C135" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D135" s="12" t="s">
-        <v>387</v>
+      <c r="D135" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>819</v>
@@ -9499,8 +9502,8 @@
       <c r="C136" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D136" s="12" t="s">
-        <v>387</v>
+      <c r="D136" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>819</v>
@@ -9542,8 +9545,8 @@
       <c r="C137" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D137" s="12" t="s">
-        <v>387</v>
+      <c r="D137" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>819</v>
@@ -9585,8 +9588,8 @@
       <c r="C138" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D138" s="12" t="s">
-        <v>387</v>
+      <c r="D138" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>819</v>
@@ -9628,8 +9631,8 @@
       <c r="C139" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="D139" s="12" t="s">
-        <v>387</v>
+      <c r="D139" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>819</v>
@@ -10012,8 +10015,8 @@
       <c r="B148" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C148" s="19" t="s">
-        <v>856</v>
+      <c r="C148" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="D148" s="12" t="s">
         <v>387</v>
@@ -10055,8 +10058,8 @@
       <c r="B149" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C149" s="19" t="s">
-        <v>856</v>
+      <c r="C149" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="D149" s="12" t="s">
         <v>387</v>
@@ -10098,8 +10101,8 @@
       <c r="B150" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C150" s="19" t="s">
-        <v>856</v>
+      <c r="C150" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="D150" s="12" t="s">
         <v>387</v>
@@ -10141,8 +10144,8 @@
       <c r="B151" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C151" s="19" t="s">
-        <v>856</v>
+      <c r="C151" s="12" t="s">
+        <v>448</v>
       </c>
       <c r="D151" s="12" t="s">
         <v>387</v>
@@ -10359,8 +10362,8 @@
       <c r="B156" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C156" s="19" t="s">
-        <v>855</v>
+      <c r="C156" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D156" s="12" t="s">
         <v>460</v>
@@ -10402,8 +10405,8 @@
       <c r="B157" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C157" s="19" t="s">
-        <v>855</v>
+      <c r="C157" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D157" s="12" t="s">
         <v>460</v>
@@ -10445,11 +10448,11 @@
       <c r="B158" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C158" s="19" t="s">
-        <v>855</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>460</v>
+      <c r="C158" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D158" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>819</v>
@@ -10488,11 +10491,11 @@
       <c r="B159" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C159" s="19" t="s">
-        <v>855</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>460</v>
+      <c r="C159" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D159" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>819</v>
@@ -10531,11 +10534,11 @@
       <c r="B160" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C160" s="19" t="s">
-        <v>855</v>
-      </c>
-      <c r="D160" s="12" t="s">
-        <v>460</v>
+      <c r="C160" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D160" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>819</v>
@@ -10574,11 +10577,11 @@
       <c r="B161" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C161" s="19" t="s">
-        <v>855</v>
-      </c>
-      <c r="D161" s="12" t="s">
-        <v>460</v>
+      <c r="C161" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D161" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>819</v>
@@ -10617,11 +10620,11 @@
       <c r="B162" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C162" s="19" t="s">
-        <v>854</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>460</v>
+      <c r="C162" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D162" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>819</v>
@@ -10660,11 +10663,11 @@
       <c r="B163" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C163" s="19" t="s">
-        <v>854</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>460</v>
+      <c r="C163" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D163" s="19" t="s">
+        <v>865</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>819</v>
@@ -10703,8 +10706,8 @@
       <c r="B164" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C164" s="19" t="s">
-        <v>854</v>
+      <c r="C164" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D164" s="12" t="s">
         <v>460</v>
@@ -10746,8 +10749,8 @@
       <c r="B165" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C165" s="19" t="s">
-        <v>854</v>
+      <c r="C165" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>460</v>
@@ -10789,8 +10792,8 @@
       <c r="B166" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C166" s="19" t="s">
-        <v>854</v>
+      <c r="C166" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>460</v>
@@ -10832,8 +10835,8 @@
       <c r="B167" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C167" s="19" t="s">
-        <v>854</v>
+      <c r="C167" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D167" s="12" t="s">
         <v>460</v>
@@ -10875,8 +10878,8 @@
       <c r="B168" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C168" s="19" t="s">
-        <v>854</v>
+      <c r="C168" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D168" s="12" t="s">
         <v>460</v>
@@ -10918,8 +10921,8 @@
       <c r="B169" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C169" s="19" t="s">
-        <v>854</v>
+      <c r="C169" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D169" s="12" t="s">
         <v>460</v>
@@ -10961,8 +10964,8 @@
       <c r="B170" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C170" s="19" t="s">
-        <v>854</v>
+      <c r="C170" s="12" t="s">
+        <v>459</v>
       </c>
       <c r="D170" s="12" t="s">
         <v>460</v>
@@ -11004,11 +11007,11 @@
       <c r="B171" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C171" s="19" t="s">
-        <v>854</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>460</v>
+      <c r="C171" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>819</v>
@@ -11047,11 +11050,11 @@
       <c r="B172" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C172" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>460</v>
+      <c r="C172" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>819</v>
@@ -11090,11 +11093,11 @@
       <c r="B173" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C173" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>460</v>
+      <c r="C173" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>819</v>
@@ -11133,11 +11136,11 @@
       <c r="B174" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C174" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>460</v>
+      <c r="C174" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>819</v>
@@ -11176,11 +11179,11 @@
       <c r="B175" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C175" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>460</v>
+      <c r="C175" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>819</v>
@@ -11219,11 +11222,11 @@
       <c r="B176" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C176" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>460</v>
+      <c r="C176" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>819</v>
@@ -11262,11 +11265,11 @@
       <c r="B177" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C177" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>460</v>
+      <c r="C177" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>819</v>
@@ -11305,11 +11308,11 @@
       <c r="B178" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C178" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>460</v>
+      <c r="C178" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>864</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>819</v>
@@ -11346,11 +11349,11 @@
       <c r="B179" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C179" s="19" t="s">
-        <v>852</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>460</v>
+      <c r="C179" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>863</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>819</v>
@@ -11389,11 +11392,11 @@
       <c r="B180" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C180" s="19" t="s">
-        <v>852</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>460</v>
+      <c r="C180" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>862</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>819</v>
@@ -11432,11 +11435,11 @@
       <c r="B181" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C181" s="19" t="s">
-        <v>852</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>460</v>
+      <c r="C181" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>861</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>819</v>
@@ -11551,6 +11554,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R1" xr:uid="{5776FB66-05B3-4E8B-A01A-C673F3C5AC7F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:K36">
     <sortCondition ref="B32:B36"/>
     <sortCondition ref="C32:C36"/>
